--- a/processed_data/hard_data_exports/hunt_tables/2026/XLXS/2026_deer_buck_limited_entry.xlsx
+++ b/processed_data/hard_data_exports/hunt_tables/2026/XLXS/2026_deer_buck_limited_entry.xlsx
@@ -2,9 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="780" yWindow="135" windowWidth="25170" windowHeight="15345" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="2026_deer_buck_limited_entry" sheetId="1" state="visible" r:id="rId1"/>
@@ -13,7 +12,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026_deer_buck_limited_entry'!$A$1:$O$68</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'2026_deer_buck_limited_entry'!$1:$1</definedName>
   </definedNames>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -29,12 +28,13 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="11"/>
     </font>
     <font>
-      <color rgb="002B1C12"/>
+      <name val="Calibri"/>
       <sz val="10"/>
     </font>
     <font>
@@ -45,10 +45,11 @@
     </font>
     <font>
       <name val="Calibri"/>
+      <color rgb="00000000"/>
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -57,16 +58,26 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="009A4E00"/>
+        <fgColor rgb="FF4F2D1D"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="004F2D1D"/>
+        <fgColor rgb="005B301B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F7F1E8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EFE5D7"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -76,48 +87,66 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00D8B58E"/>
+        <color rgb="FFD8B58E"/>
       </left>
       <right style="thin">
-        <color rgb="00D8B58E"/>
+        <color rgb="FFD8B58E"/>
       </right>
       <top style="thin">
-        <color rgb="00D8B58E"/>
+        <color rgb="FFD8B58E"/>
       </top>
       <bottom style="thin">
-        <color rgb="00D8B58E"/>
+        <color rgb="FFD8B58E"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C58F61"/>
+      </left>
+      <right style="thin">
+        <color rgb="00C58F61"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C58F61"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C58F61"/>
       </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -507,132 +536,132 @@
   <dimension ref="A1:O68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="36" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="36" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="20" customWidth="1" min="12" max="12"/>
-    <col width="36" customWidth="1" min="13" max="13"/>
-    <col width="36" customWidth="1" min="14" max="14"/>
-    <col width="36" customWidth="1" min="15" max="15"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="4"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="10"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="24" customWidth="1" min="13" max="15"/>
+    <col width="24" customWidth="1" min="14" max="14"/>
+    <col width="24" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="3" t="inlineStr">
+    <row r="1" ht="27.95" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>hunt_name</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>hunt_code</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>sex_type</t>
         </is>
       </c>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="D1" s="4" t="inlineStr">
         <is>
           <t>species</t>
         </is>
       </c>
-      <c r="E1" s="3" t="inlineStr">
+      <c r="E1" s="4" t="inlineStr">
         <is>
           <t>weapon</t>
         </is>
       </c>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="F1" s="4" t="inlineStr">
         <is>
           <t>hunt_type</t>
         </is>
       </c>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="G1" s="4" t="inlineStr">
         <is>
           <t>season</t>
         </is>
       </c>
-      <c r="H1" s="3" t="inlineStr">
+      <c r="H1" s="4" t="inlineStr">
         <is>
           <t>permits_2026_res</t>
         </is>
       </c>
-      <c r="I1" s="3" t="inlineStr">
+      <c r="I1" s="4" t="inlineStr">
         <is>
           <t>permits_2026_nr</t>
         </is>
       </c>
-      <c r="J1" s="3" t="inlineStr">
+      <c r="J1" s="4" t="inlineStr">
         <is>
           <t>permits_2026_total</t>
         </is>
       </c>
-      <c r="K1" s="3" t="inlineStr">
+      <c r="K1" s="4" t="inlineStr">
         <is>
           <t>NOTES</t>
         </is>
       </c>
-      <c r="L1" s="3" t="inlineStr">
+      <c r="L1" s="4" t="inlineStr">
         <is>
           <t>Harvest Prior Year</t>
         </is>
       </c>
-      <c r="M1" s="3" t="inlineStr">
+      <c r="M1" s="4" t="inlineStr">
         <is>
           <t>Percent Harvest Success (previous hunting season)</t>
         </is>
       </c>
-      <c r="N1" s="3" t="inlineStr">
+      <c r="N1" s="4" t="inlineStr">
         <is>
           <t>Average Age Harvested (previous hunting season)</t>
         </is>
       </c>
-      <c r="O1" s="3" t="inlineStr">
+      <c r="O1" s="4" t="inlineStr">
         <is>
           <t>Avg Days Hunted (previous hunting season)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="24" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>Book Cliffs</t>
         </is>
       </c>
-      <c r="B2" s="6" t="inlineStr">
+      <c r="B2" s="5" t="inlineStr">
         <is>
           <t>DB1011</t>
         </is>
       </c>
-      <c r="C2" s="6" t="inlineStr">
-        <is>
-          <t>Buck</t>
-        </is>
-      </c>
-      <c r="D2" s="6" t="inlineStr">
-        <is>
-          <t>Deer</t>
-        </is>
-      </c>
-      <c r="E2" s="6" t="inlineStr">
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Buck</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>Deer</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
         <is>
           <t>Archery</t>
         </is>
       </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>Limited Entry</t>
-        </is>
-      </c>
-      <c r="G2" s="6" t="inlineStr">
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>Limited Entry</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
         <is>
           <t>Aug 15 2026 - Sept 11 2026</t>
         </is>
@@ -642,7 +671,7 @@
           <t>55</t>
         </is>
       </c>
-      <c r="I2" s="6" t="inlineStr">
+      <c r="I2" s="5" t="inlineStr">
         <is>
           <t>6</t>
         </is>
@@ -652,121 +681,121 @@
           <t>61</t>
         </is>
       </c>
-      <c r="K2" s="6" t="inlineStr"/>
-      <c r="L2" s="7" t="n">
-        <v>2025</v>
-      </c>
-      <c r="M2" s="7" t="inlineStr">
+      <c r="K2" s="5" t="n"/>
+      <c r="L2" s="5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="M2" s="6" t="inlineStr">
         <is>
           <t>88</t>
         </is>
       </c>
-      <c r="N2" s="7" t="inlineStr"/>
-      <c r="O2" s="7" t="inlineStr">
+      <c r="N2" s="6" t="n"/>
+      <c r="O2" s="6" t="inlineStr">
         <is>
           <t>6.6</t>
         </is>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>Fillmore, Oak Creek LE</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B3" s="7" t="inlineStr">
         <is>
           <t>DB1012</t>
         </is>
       </c>
-      <c r="C3" s="6" t="inlineStr">
-        <is>
-          <t>Buck</t>
-        </is>
-      </c>
-      <c r="D3" s="6" t="inlineStr">
-        <is>
-          <t>Deer</t>
-        </is>
-      </c>
-      <c r="E3" s="6" t="inlineStr">
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>Buck</t>
+        </is>
+      </c>
+      <c r="D3" s="7" t="inlineStr">
+        <is>
+          <t>Deer</t>
+        </is>
+      </c>
+      <c r="E3" s="7" t="inlineStr">
         <is>
           <t>Archery</t>
         </is>
       </c>
-      <c r="F3" s="6" t="inlineStr">
-        <is>
-          <t>Limited Entry</t>
-        </is>
-      </c>
-      <c r="G3" s="6" t="inlineStr">
+      <c r="F3" s="7" t="inlineStr">
+        <is>
+          <t>Limited Entry</t>
+        </is>
+      </c>
+      <c r="G3" s="7" t="inlineStr">
         <is>
           <t>Aug 15 2026 - Sept 11 2026</t>
         </is>
       </c>
-      <c r="H3" s="6" t="inlineStr">
+      <c r="H3" s="8" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="I3" s="6" t="inlineStr">
+      <c r="I3" s="7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="J3" s="6" t="inlineStr">
+      <c r="J3" s="8" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="K3" s="6" t="inlineStr"/>
+      <c r="K3" s="7" t="n"/>
       <c r="L3" s="7" t="n">
         <v>2025</v>
       </c>
-      <c r="M3" s="7" t="inlineStr">
+      <c r="M3" s="8" t="inlineStr">
         <is>
           <t>84.6</t>
         </is>
       </c>
-      <c r="N3" s="7" t="inlineStr"/>
-      <c r="O3" s="7" t="inlineStr">
+      <c r="N3" s="8" t="n"/>
+      <c r="O3" s="8" t="inlineStr">
         <is>
           <t>9.2</t>
         </is>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>Dolores Triangle</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>DB1013</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>Buck</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>Deer</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>Buck</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>Deer</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>Archery</t>
         </is>
       </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>Limited Entry</t>
-        </is>
-      </c>
-      <c r="G4" s="6" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>Limited Entry</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>Oct 31 2026 - Nov 13 2026</t>
         </is>
@@ -776,7 +805,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="I4" s="6" t="inlineStr">
+      <c r="I4" s="5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -786,121 +815,121 @@
           <t>5</t>
         </is>
       </c>
-      <c r="K4" s="6" t="inlineStr"/>
-      <c r="L4" s="7" t="n">
-        <v>2025</v>
-      </c>
-      <c r="M4" s="7" t="inlineStr">
+      <c r="K4" s="5" t="n"/>
+      <c r="L4" s="5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="M4" s="6" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="N4" s="7" t="inlineStr"/>
-      <c r="O4" s="7" t="inlineStr">
+      <c r="N4" s="6" t="n"/>
+      <c r="O4" s="6" t="inlineStr">
         <is>
           <t>7.5</t>
         </is>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>San Juan, Elk Ridge</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>DB1014</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>Buck</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>Deer</t>
-        </is>
-      </c>
-      <c r="E5" s="6" t="inlineStr">
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>Buck</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>Deer</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
         <is>
           <t>Archery</t>
         </is>
       </c>
-      <c r="F5" s="6" t="inlineStr">
-        <is>
-          <t>Limited Entry</t>
-        </is>
-      </c>
-      <c r="G5" s="6" t="inlineStr">
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>Limited Entry</t>
+        </is>
+      </c>
+      <c r="G5" s="7" t="inlineStr">
         <is>
           <t>Aug 15 2026 - Sept 11 2026</t>
         </is>
       </c>
-      <c r="H5" s="6" t="inlineStr">
+      <c r="H5" s="8" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="I5" s="6" t="inlineStr">
+      <c r="I5" s="7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="J5" s="6" t="inlineStr">
+      <c r="J5" s="8" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="K5" s="6" t="inlineStr"/>
+      <c r="K5" s="7" t="n"/>
       <c r="L5" s="7" t="n">
         <v>2025</v>
       </c>
-      <c r="M5" s="7" t="inlineStr">
+      <c r="M5" s="8" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="N5" s="7" t="inlineStr"/>
-      <c r="O5" s="7" t="inlineStr">
+      <c r="N5" s="8" t="n"/>
+      <c r="O5" s="8" t="inlineStr">
         <is>
           <t>5.3</t>
         </is>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>Diamond Mtn</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>DB1015</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>Buck</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>Deer</t>
-        </is>
-      </c>
-      <c r="E6" s="6" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Buck</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>Deer</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>Archery</t>
         </is>
       </c>
-      <c r="F6" s="6" t="inlineStr">
-        <is>
-          <t>Limited Entry</t>
-        </is>
-      </c>
-      <c r="G6" s="6" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>Limited Entry</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>Aug 15 2026 - Sept 11 2026</t>
         </is>
@@ -910,7 +939,7 @@
           <t>22</t>
         </is>
       </c>
-      <c r="I6" s="6" t="inlineStr">
+      <c r="I6" s="5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -920,121 +949,121 @@
           <t>24</t>
         </is>
       </c>
-      <c r="K6" s="6" t="inlineStr"/>
-      <c r="L6" s="7" t="n">
-        <v>2025</v>
-      </c>
-      <c r="M6" s="7" t="inlineStr">
+      <c r="K6" s="5" t="n"/>
+      <c r="L6" s="5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="M6" s="6" t="inlineStr">
         <is>
           <t>86.4</t>
         </is>
       </c>
-      <c r="N6" s="7" t="inlineStr"/>
-      <c r="O6" s="7" t="inlineStr">
+      <c r="N6" s="6" t="n"/>
+      <c r="O6" s="6" t="inlineStr">
         <is>
           <t>7.6</t>
         </is>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>West Desert, Vernon</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>DB1016</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>Buck</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>Deer</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>Buck</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>Deer</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
         <is>
           <t>Archery</t>
         </is>
       </c>
-      <c r="F7" s="6" t="inlineStr">
-        <is>
-          <t>Limited Entry</t>
-        </is>
-      </c>
-      <c r="G7" s="6" t="inlineStr">
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>Limited Entry</t>
+        </is>
+      </c>
+      <c r="G7" s="7" t="inlineStr">
         <is>
           <t>Aug 15 2026 - Sept 11 2026</t>
         </is>
       </c>
-      <c r="H7" s="6" t="inlineStr">
+      <c r="H7" s="8" t="inlineStr">
         <is>
           <t>46</t>
         </is>
       </c>
-      <c r="I7" s="6" t="inlineStr">
+      <c r="I7" s="7" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="J7" s="6" t="inlineStr">
+      <c r="J7" s="8" t="inlineStr">
         <is>
           <t>51</t>
         </is>
       </c>
-      <c r="K7" s="6" t="inlineStr"/>
+      <c r="K7" s="7" t="n"/>
       <c r="L7" s="7" t="n">
         <v>2025</v>
       </c>
-      <c r="M7" s="7" t="inlineStr">
+      <c r="M7" s="8" t="inlineStr">
         <is>
           <t>56.9</t>
         </is>
       </c>
-      <c r="N7" s="7" t="inlineStr"/>
-      <c r="O7" s="7" t="inlineStr">
+      <c r="N7" s="8" t="n"/>
+      <c r="O7" s="8" t="inlineStr">
         <is>
           <t>8.8</t>
         </is>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>Book Cliffs, North</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>DB1017</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>Buck</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>Deer</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Buck</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>Deer</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>Any Legal Weapon</t>
         </is>
       </c>
-      <c r="F8" s="6" t="inlineStr">
-        <is>
-          <t>Limited Entry</t>
-        </is>
-      </c>
-      <c r="G8" s="6" t="inlineStr">
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>Limited Entry</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
         <is>
           <t>Oct 17 2026 - Oct 25 2026</t>
         </is>
@@ -1044,7 +1073,7 @@
           <t>137</t>
         </is>
       </c>
-      <c r="I8" s="6" t="inlineStr">
+      <c r="I8" s="5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
@@ -1054,121 +1083,121 @@
           <t>152</t>
         </is>
       </c>
-      <c r="K8" s="6" t="inlineStr"/>
-      <c r="L8" s="7" t="n">
-        <v>2025</v>
-      </c>
-      <c r="M8" s="7" t="inlineStr">
+      <c r="K8" s="5" t="n"/>
+      <c r="L8" s="5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="M8" s="6" t="inlineStr">
         <is>
           <t>93.6</t>
         </is>
       </c>
-      <c r="N8" s="7" t="inlineStr"/>
-      <c r="O8" s="7" t="inlineStr">
+      <c r="N8" s="6" t="n"/>
+      <c r="O8" s="6" t="inlineStr">
         <is>
           <t>3.7</t>
         </is>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>Book Cliffs, South</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
+      <c r="B9" s="7" t="inlineStr">
         <is>
           <t>DB1018</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>Buck</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>Deer</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="inlineStr">
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>Buck</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>Deer</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
         <is>
           <t>Any Legal Weapon</t>
         </is>
       </c>
-      <c r="F9" s="6" t="inlineStr">
-        <is>
-          <t>Limited Entry</t>
-        </is>
-      </c>
-      <c r="G9" s="6" t="inlineStr">
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>Limited Entry</t>
+        </is>
+      </c>
+      <c r="G9" s="7" t="inlineStr">
         <is>
           <t>Oct 17 2026 - Oct 25 2026</t>
         </is>
       </c>
-      <c r="H9" s="6" t="inlineStr">
+      <c r="H9" s="8" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="I9" s="6" t="inlineStr">
+      <c r="I9" s="7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J9" s="6" t="inlineStr">
+      <c r="J9" s="8" t="inlineStr">
         <is>
           <t>38</t>
         </is>
       </c>
-      <c r="K9" s="6" t="inlineStr"/>
+      <c r="K9" s="7" t="n"/>
       <c r="L9" s="7" t="n">
         <v>2025</v>
       </c>
-      <c r="M9" s="7" t="inlineStr">
+      <c r="M9" s="8" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="N9" s="7" t="inlineStr"/>
-      <c r="O9" s="7" t="inlineStr">
+      <c r="N9" s="8" t="n"/>
+      <c r="O9" s="8" t="inlineStr">
         <is>
           <t>3.7</t>
         </is>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>Fillmore, Oak Creek LE</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>DB1019</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>Buck</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>Deer</t>
-        </is>
-      </c>
-      <c r="E10" s="6" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Buck</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>Deer</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
         <is>
           <t>Any Legal Weapon</t>
         </is>
       </c>
-      <c r="F10" s="6" t="inlineStr">
-        <is>
-          <t>Limited Entry</t>
-        </is>
-      </c>
-      <c r="G10" s="6" t="inlineStr">
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>Limited Entry</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
         <is>
           <t>Oct 17 2026 - Oct 25 2026</t>
         </is>
@@ -1178,7 +1207,7 @@
           <t>33</t>
         </is>
       </c>
-      <c r="I10" s="6" t="inlineStr">
+      <c r="I10" s="5" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -1188,121 +1217,121 @@
           <t>37</t>
         </is>
       </c>
-      <c r="K10" s="6" t="inlineStr"/>
-      <c r="L10" s="7" t="n">
-        <v>2025</v>
-      </c>
-      <c r="M10" s="7" t="inlineStr">
+      <c r="K10" s="5" t="n"/>
+      <c r="L10" s="5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="M10" s="6" t="inlineStr">
         <is>
           <t>95</t>
         </is>
       </c>
-      <c r="N10" s="7" t="inlineStr"/>
-      <c r="O10" s="7" t="inlineStr">
+      <c r="N10" s="6" t="n"/>
+      <c r="O10" s="6" t="inlineStr">
         <is>
           <t>4.4</t>
         </is>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>Dolores Triangle</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B11" s="7" t="inlineStr">
         <is>
           <t>DB1020</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>Buck</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>Deer</t>
-        </is>
-      </c>
-      <c r="E11" s="6" t="inlineStr">
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>Buck</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>Deer</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
         <is>
           <t>Any Legal Weapon</t>
         </is>
       </c>
-      <c r="F11" s="6" t="inlineStr">
-        <is>
-          <t>Limited Entry</t>
-        </is>
-      </c>
-      <c r="G11" s="6" t="inlineStr">
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>Limited Entry</t>
+        </is>
+      </c>
+      <c r="G11" s="7" t="inlineStr">
         <is>
           <t>Nov 14 2026 - Nov 22 2026</t>
         </is>
       </c>
-      <c r="H11" s="6" t="inlineStr">
+      <c r="H11" s="8" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="I11" s="6" t="inlineStr">
+      <c r="I11" s="7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="J11" s="6" t="inlineStr">
+      <c r="J11" s="8" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="K11" s="6" t="inlineStr"/>
+      <c r="K11" s="7" t="n"/>
       <c r="L11" s="7" t="n">
         <v>2025</v>
       </c>
-      <c r="M11" s="7" t="inlineStr">
+      <c r="M11" s="8" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="N11" s="7" t="inlineStr"/>
-      <c r="O11" s="7" t="inlineStr">
+      <c r="N11" s="8" t="n"/>
+      <c r="O11" s="8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>San Juan, Elk Ridge</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>DB1022</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>Buck</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>Deer</t>
-        </is>
-      </c>
-      <c r="E12" s="6" t="inlineStr">
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Buck</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>Deer</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
         <is>
           <t>Any Legal Weapon</t>
         </is>
       </c>
-      <c r="F12" s="6" t="inlineStr">
-        <is>
-          <t>Limited Entry</t>
-        </is>
-      </c>
-      <c r="G12" s="6" t="inlineStr">
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>Limited Entry</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
         <is>
           <t>Oct 17 2026 - Oct 25 2026</t>
         </is>
@@ -1312,7 +1341,7 @@
           <t>42</t>
         </is>
       </c>
-      <c r="I12" s="6" t="inlineStr">
+      <c r="I12" s="5" t="inlineStr">
         <is>
           <t>5</t>
         </is>
@@ -1322,121 +1351,121 @@
           <t>47</t>
         </is>
       </c>
-      <c r="K12" s="6" t="inlineStr"/>
-      <c r="L12" s="7" t="n">
-        <v>2025</v>
-      </c>
-      <c r="M12" s="7" t="inlineStr">
+      <c r="K12" s="5" t="n"/>
+      <c r="L12" s="5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="M12" s="6" t="inlineStr">
         <is>
           <t>88.9</t>
         </is>
       </c>
-      <c r="N12" s="7" t="inlineStr"/>
-      <c r="O12" s="7" t="inlineStr">
+      <c r="N12" s="6" t="n"/>
+      <c r="O12" s="6" t="inlineStr">
         <is>
           <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1">
-      <c r="A13" s="6" t="inlineStr">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>Diamond Mtn</t>
         </is>
       </c>
-      <c r="B13" s="6" t="inlineStr">
+      <c r="B13" s="7" t="inlineStr">
         <is>
           <t>DB1023</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>Buck</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="inlineStr">
-        <is>
-          <t>Deer</t>
-        </is>
-      </c>
-      <c r="E13" s="6" t="inlineStr">
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>Buck</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>Deer</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
         <is>
           <t>Any Legal Weapon</t>
         </is>
       </c>
-      <c r="F13" s="6" t="inlineStr">
-        <is>
-          <t>Limited Entry</t>
-        </is>
-      </c>
-      <c r="G13" s="6" t="inlineStr">
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>Limited Entry</t>
+        </is>
+      </c>
+      <c r="G13" s="7" t="inlineStr">
         <is>
           <t>Oct 17 2026 - Oct 25 2026</t>
         </is>
       </c>
-      <c r="H13" s="6" t="inlineStr">
+      <c r="H13" s="8" t="inlineStr">
         <is>
           <t>61</t>
         </is>
       </c>
-      <c r="I13" s="6" t="inlineStr">
+      <c r="I13" s="7" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="J13" s="6" t="inlineStr">
+      <c r="J13" s="8" t="inlineStr">
         <is>
           <t>68</t>
         </is>
       </c>
-      <c r="K13" s="6" t="inlineStr"/>
+      <c r="K13" s="7" t="n"/>
       <c r="L13" s="7" t="n">
         <v>2025</v>
       </c>
-      <c r="M13" s="7" t="inlineStr">
+      <c r="M13" s="8" t="inlineStr">
         <is>
           <t>96.9</t>
         </is>
       </c>
-      <c r="N13" s="7" t="inlineStr"/>
-      <c r="O13" s="7" t="inlineStr">
+      <c r="N13" s="8" t="n"/>
+      <c r="O13" s="8" t="inlineStr">
         <is>
           <t>3.4</t>
         </is>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1">
-      <c r="A14" s="6" t="inlineStr">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>West Desert, Vernon</t>
         </is>
       </c>
-      <c r="B14" s="6" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>DB1024</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>Buck</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="inlineStr">
-        <is>
-          <t>Deer</t>
-        </is>
-      </c>
-      <c r="E14" s="6" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>Buck</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>Deer</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
         <is>
           <t>Any Legal Weapon</t>
         </is>
       </c>
-      <c r="F14" s="6" t="inlineStr">
-        <is>
-          <t>Limited Entry</t>
-        </is>
-      </c>
-      <c r="G14" s="6" t="inlineStr">
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>Limited Entry</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
         <is>
           <t>Oct 17 2026 - Oct 25 2026</t>
         </is>
@@ -1446,7 +1475,7 @@
           <t>130</t>
         </is>
       </c>
-      <c r="I14" s="6" t="inlineStr">
+      <c r="I14" s="5" t="inlineStr">
         <is>
           <t>14</t>
         </is>
@@ -1456,121 +1485,121 @@
           <t>144</t>
         </is>
       </c>
-      <c r="K14" s="6" t="inlineStr"/>
-      <c r="L14" s="7" t="n">
-        <v>2025</v>
-      </c>
-      <c r="M14" s="7" t="inlineStr">
+      <c r="K14" s="5" t="n"/>
+      <c r="L14" s="5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="M14" s="6" t="inlineStr">
         <is>
           <t>85.4</t>
         </is>
       </c>
-      <c r="N14" s="7" t="inlineStr"/>
-      <c r="O14" s="7" t="inlineStr">
+      <c r="N14" s="6" t="n"/>
+      <c r="O14" s="6" t="inlineStr">
         <is>
           <t>4.4</t>
         </is>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1">
-      <c r="A15" s="6" t="inlineStr">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t>Book Cliffs</t>
         </is>
       </c>
-      <c r="B15" s="6" t="inlineStr">
+      <c r="B15" s="7" t="inlineStr">
         <is>
           <t>DB1025</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>Buck</t>
-        </is>
-      </c>
-      <c r="D15" s="6" t="inlineStr">
-        <is>
-          <t>Deer</t>
-        </is>
-      </c>
-      <c r="E15" s="6" t="inlineStr">
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>Buck</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>Deer</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
         <is>
           <t>Muzzleloader</t>
         </is>
       </c>
-      <c r="F15" s="6" t="inlineStr">
-        <is>
-          <t>Limited Entry</t>
-        </is>
-      </c>
-      <c r="G15" s="6" t="inlineStr">
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>Limited Entry</t>
+        </is>
+      </c>
+      <c r="G15" s="7" t="inlineStr">
         <is>
           <t>Sept 23 2026 - Oct 01 2026</t>
         </is>
       </c>
-      <c r="H15" s="6" t="inlineStr">
+      <c r="H15" s="8" t="inlineStr">
         <is>
           <t>55</t>
         </is>
       </c>
-      <c r="I15" s="6" t="inlineStr">
+      <c r="I15" s="7" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="J15" s="6" t="inlineStr">
+      <c r="J15" s="8" t="inlineStr">
         <is>
           <t>61</t>
         </is>
       </c>
-      <c r="K15" s="6" t="inlineStr"/>
+      <c r="K15" s="7" t="n"/>
       <c r="L15" s="7" t="n">
         <v>2025</v>
       </c>
-      <c r="M15" s="7" t="inlineStr">
+      <c r="M15" s="8" t="inlineStr">
         <is>
           <t>86</t>
         </is>
       </c>
-      <c r="N15" s="7" t="inlineStr"/>
-      <c r="O15" s="7" t="inlineStr">
+      <c r="N15" s="8" t="n"/>
+      <c r="O15" s="8" t="inlineStr">
         <is>
           <t>3.8</t>
         </is>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1">
-      <c r="A16" s="6" t="inlineStr">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>Cache, Crawford Mtn</t>
         </is>
       </c>
-      <c r="B16" s="6" t="inlineStr">
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>DB1026</t>
         </is>
       </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>Buck</t>
-        </is>
-      </c>
-      <c r="D16" s="6" t="inlineStr">
-        <is>
-          <t>Deer</t>
-        </is>
-      </c>
-      <c r="E16" s="6" t="inlineStr">
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>Buck</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>Deer</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
         <is>
           <t>Muzzleloader</t>
         </is>
       </c>
-      <c r="F16" s="6" t="inlineStr">
-        <is>
-          <t>Limited Entry</t>
-        </is>
-      </c>
-      <c r="G16" s="6" t="inlineStr">
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>Limited Entry</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
         <is>
           <t>Nov 07 2026 - Nov 22 2026</t>
         </is>
@@ -1580,7 +1609,7 @@
           <t>8</t>
         </is>
       </c>
-      <c r="I16" s="6" t="inlineStr">
+      <c r="I16" s="5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -1590,121 +1619,121 @@
           <t>9</t>
         </is>
       </c>
-      <c r="K16" s="6" t="inlineStr"/>
-      <c r="L16" s="7" t="n">
-        <v>2025</v>
-      </c>
-      <c r="M16" s="7" t="inlineStr">
+      <c r="K16" s="5" t="n"/>
+      <c r="L16" s="5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="M16" s="6" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="N16" s="7" t="inlineStr"/>
-      <c r="O16" s="7" t="inlineStr">
+      <c r="N16" s="6" t="n"/>
+      <c r="O16" s="6" t="inlineStr">
         <is>
           <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1">
-      <c r="A17" s="6" t="inlineStr">
+      <c r="A17" s="7" t="inlineStr">
         <is>
           <t>Fillmore</t>
         </is>
       </c>
-      <c r="B17" s="6" t="inlineStr">
+      <c r="B17" s="7" t="inlineStr">
         <is>
           <t>DB1028</t>
         </is>
       </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>Buck</t>
-        </is>
-      </c>
-      <c r="D17" s="6" t="inlineStr">
-        <is>
-          <t>Deer</t>
-        </is>
-      </c>
-      <c r="E17" s="6" t="inlineStr">
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>Buck</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>Deer</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
         <is>
           <t>Muzzleloader</t>
         </is>
       </c>
-      <c r="F17" s="6" t="inlineStr">
-        <is>
-          <t>Limited Entry</t>
-        </is>
-      </c>
-      <c r="G17" s="6" t="inlineStr">
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>Limited Entry</t>
+        </is>
+      </c>
+      <c r="G17" s="7" t="inlineStr">
         <is>
           <t>Oct 28 2026 - Nov 05 2026</t>
         </is>
       </c>
-      <c r="H17" s="6" t="inlineStr">
+      <c r="H17" s="8" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="I17" s="6" t="inlineStr">
+      <c r="I17" s="7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="J17" s="6" t="inlineStr">
+      <c r="J17" s="8" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="K17" s="6" t="inlineStr"/>
+      <c r="K17" s="7" t="n"/>
       <c r="L17" s="7" t="n">
         <v>2025</v>
       </c>
-      <c r="M17" s="7" t="inlineStr">
+      <c r="M17" s="8" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="N17" s="7" t="inlineStr"/>
-      <c r="O17" s="7" t="inlineStr">
+      <c r="N17" s="8" t="n"/>
+      <c r="O17" s="8" t="inlineStr">
         <is>
           <t>7.2</t>
         </is>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1">
-      <c r="A18" s="6" t="inlineStr">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>Fillmore, Oak Creek LE</t>
         </is>
       </c>
-      <c r="B18" s="6" t="inlineStr">
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>DB1029</t>
         </is>
       </c>
-      <c r="C18" s="6" t="inlineStr">
-        <is>
-          <t>Buck</t>
-        </is>
-      </c>
-      <c r="D18" s="6" t="inlineStr">
-        <is>
-          <t>Deer</t>
-        </is>
-      </c>
-      <c r="E18" s="6" t="inlineStr">
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>Buck</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>Deer</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
         <is>
           <t>Muzzleloader</t>
         </is>
       </c>
-      <c r="F18" s="6" t="inlineStr">
-        <is>
-          <t>Limited Entry</t>
-        </is>
-      </c>
-      <c r="G18" s="6" t="inlineStr">
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>Limited Entry</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
         <is>
           <t>Sept 23 2026 - Oct 01 2026</t>
         </is>
@@ -1714,7 +1743,7 @@
           <t>12</t>
         </is>
       </c>
-      <c r="I18" s="6" t="inlineStr">
+      <c r="I18" s="5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -1724,121 +1753,121 @@
           <t>13</t>
         </is>
       </c>
-      <c r="K18" s="6" t="inlineStr"/>
-      <c r="L18" s="7" t="n">
-        <v>2025</v>
-      </c>
-      <c r="M18" s="7" t="inlineStr">
+      <c r="K18" s="5" t="n"/>
+      <c r="L18" s="5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="M18" s="6" t="inlineStr">
         <is>
           <t>80</t>
         </is>
       </c>
-      <c r="N18" s="7" t="inlineStr"/>
-      <c r="O18" s="7" t="inlineStr">
+      <c r="N18" s="6" t="n"/>
+      <c r="O18" s="6" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1">
-      <c r="A19" s="6" t="inlineStr">
+      <c r="A19" s="7" t="inlineStr">
         <is>
           <t>Kamas</t>
         </is>
       </c>
-      <c r="B19" s="6" t="inlineStr">
+      <c r="B19" s="7" t="inlineStr">
         <is>
           <t>DB1030</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr">
-        <is>
-          <t>Buck</t>
-        </is>
-      </c>
-      <c r="D19" s="6" t="inlineStr">
-        <is>
-          <t>Deer</t>
-        </is>
-      </c>
-      <c r="E19" s="6" t="inlineStr">
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>Buck</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>Deer</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
         <is>
           <t>Muzzleloader</t>
         </is>
       </c>
-      <c r="F19" s="6" t="inlineStr">
-        <is>
-          <t>Limited Entry</t>
-        </is>
-      </c>
-      <c r="G19" s="6" t="inlineStr">
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>Limited Entry</t>
+        </is>
+      </c>
+      <c r="G19" s="7" t="inlineStr">
         <is>
           <t>Oct 28 2026 - Nov 05 2026</t>
         </is>
       </c>
-      <c r="H19" s="6" t="inlineStr">
+      <c r="H19" s="8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="I19" s="6" t="inlineStr">
+      <c r="I19" s="7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="J19" s="6" t="inlineStr">
+      <c r="J19" s="8" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="K19" s="6" t="inlineStr"/>
+      <c r="K19" s="7" t="n"/>
       <c r="L19" s="7" t="n">
         <v>2025</v>
       </c>
-      <c r="M19" s="7" t="inlineStr">
+      <c r="M19" s="8" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="N19" s="7" t="inlineStr"/>
-      <c r="O19" s="7" t="inlineStr">
+      <c r="N19" s="8" t="n"/>
+      <c r="O19" s="8" t="inlineStr">
         <is>
           <t>5.5</t>
         </is>
       </c>
     </row>
     <row r="20" ht="24" customHeight="1">
-      <c r="A20" s="6" t="inlineStr">
+      <c r="A20" s="5" t="inlineStr">
         <is>
           <t>Dolores Triangle</t>
         </is>
       </c>
-      <c r="B20" s="6" t="inlineStr">
+      <c r="B20" s="5" t="inlineStr">
         <is>
           <t>DB1031</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr">
-        <is>
-          <t>Buck</t>
-        </is>
-      </c>
-      <c r="D20" s="6" t="inlineStr">
-        <is>
-          <t>Deer</t>
-        </is>
-      </c>
-      <c r="E20" s="6" t="inlineStr">
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>Buck</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>Deer</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
         <is>
           <t>Muzzleloader</t>
         </is>
       </c>
-      <c r="F20" s="6" t="inlineStr">
-        <is>
-          <t>Limited Entry</t>
-        </is>
-      </c>
-      <c r="G20" s="6" t="inlineStr">
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>Limited Entry</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
         <is>
           <t>Nov 23 2026 - Dec 01 2026</t>
         </is>
@@ -1848,7 +1877,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="I20" s="6" t="inlineStr">
+      <c r="I20" s="5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1858,121 +1887,121 @@
           <t>5</t>
         </is>
       </c>
-      <c r="K20" s="6" t="inlineStr"/>
-      <c r="L20" s="7" t="n">
-        <v>2025</v>
-      </c>
-      <c r="M20" s="7" t="inlineStr">
+      <c r="K20" s="5" t="n"/>
+      <c r="L20" s="5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="M20" s="6" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="N20" s="7" t="inlineStr"/>
-      <c r="O20" s="7" t="inlineStr">
+      <c r="N20" s="6" t="n"/>
+      <c r="O20" s="6" t="inlineStr">
         <is>
           <t>6.5</t>
         </is>
       </c>
     </row>
     <row r="21" ht="24" customHeight="1">
-      <c r="A21" s="6" t="inlineStr">
+      <c r="A21" s="7" t="inlineStr">
         <is>
           <t>Monroe</t>
         </is>
       </c>
-      <c r="B21" s="6" t="inlineStr">
+      <c r="B21" s="7" t="inlineStr">
         <is>
           <t>DB1032</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr">
-        <is>
-          <t>Buck</t>
-        </is>
-      </c>
-      <c r="D21" s="6" t="inlineStr">
-        <is>
-          <t>Deer</t>
-        </is>
-      </c>
-      <c r="E21" s="6" t="inlineStr">
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>Buck</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>Deer</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
         <is>
           <t>Muzzleloader</t>
         </is>
       </c>
-      <c r="F21" s="6" t="inlineStr">
-        <is>
-          <t>Limited Entry</t>
-        </is>
-      </c>
-      <c r="G21" s="6" t="inlineStr">
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>Limited Entry</t>
+        </is>
+      </c>
+      <c r="G21" s="7" t="inlineStr">
         <is>
           <t>Oct 28 2026 - Nov 05 2026</t>
         </is>
       </c>
-      <c r="H21" s="6" t="inlineStr">
+      <c r="H21" s="8" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="I21" s="6" t="inlineStr">
+      <c r="I21" s="7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="J21" s="6" t="inlineStr">
+      <c r="J21" s="8" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="K21" s="6" t="inlineStr"/>
+      <c r="K21" s="7" t="n"/>
       <c r="L21" s="7" t="n">
         <v>2025</v>
       </c>
-      <c r="M21" s="7" t="inlineStr">
+      <c r="M21" s="8" t="inlineStr">
         <is>
           <t>66.7</t>
         </is>
       </c>
-      <c r="N21" s="7" t="inlineStr"/>
-      <c r="O21" s="7" t="inlineStr">
+      <c r="N21" s="8" t="n"/>
+      <c r="O21" s="8" t="inlineStr">
         <is>
           <t>6.5</t>
         </is>
       </c>
     </row>
     <row r="22" ht="24" customHeight="1">
-      <c r="A22" s="6" t="inlineStr">
+      <c r="A22" s="5" t="inlineStr">
         <is>
           <t>Nine Mile</t>
         </is>
       </c>
-      <c r="B22" s="6" t="inlineStr">
+      <c r="B22" s="5" t="inlineStr">
         <is>
           <t>DB1033</t>
         </is>
       </c>
-      <c r="C22" s="6" t="inlineStr">
-        <is>
-          <t>Buck</t>
-        </is>
-      </c>
-      <c r="D22" s="6" t="inlineStr">
-        <is>
-          <t>Deer</t>
-        </is>
-      </c>
-      <c r="E22" s="6" t="inlineStr">
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>Buck</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>Deer</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
         <is>
           <t>Muzzleloader</t>
         </is>
       </c>
-      <c r="F22" s="6" t="inlineStr">
-        <is>
-          <t>Limited Entry</t>
-        </is>
-      </c>
-      <c r="G22" s="6" t="inlineStr">
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>Limited Entry</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="inlineStr">
         <is>
           <t>Oct 28 2026 - Nov 05 2026</t>
         </is>
@@ -1982,7 +2011,7 @@
           <t>6</t>
         </is>
       </c>
-      <c r="I22" s="6" t="inlineStr">
+      <c r="I22" s="5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -1992,121 +2021,121 @@
           <t>7</t>
         </is>
       </c>
-      <c r="K22" s="6" t="inlineStr"/>
-      <c r="L22" s="7" t="n">
-        <v>2025</v>
-      </c>
-      <c r="M22" s="7" t="inlineStr">
+      <c r="K22" s="5" t="n"/>
+      <c r="L22" s="5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="M22" s="6" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="N22" s="7" t="inlineStr"/>
-      <c r="O22" s="7" t="inlineStr">
+      <c r="N22" s="6" t="n"/>
+      <c r="O22" s="6" t="inlineStr">
         <is>
           <t>4.5</t>
         </is>
       </c>
     </row>
     <row r="23" ht="24" customHeight="1">
-      <c r="A23" s="6" t="inlineStr">
+      <c r="A23" s="7" t="inlineStr">
         <is>
           <t>Pine Valley</t>
         </is>
       </c>
-      <c r="B23" s="6" t="inlineStr">
+      <c r="B23" s="7" t="inlineStr">
         <is>
           <t>DB1034</t>
         </is>
       </c>
-      <c r="C23" s="6" t="inlineStr">
-        <is>
-          <t>Buck</t>
-        </is>
-      </c>
-      <c r="D23" s="6" t="inlineStr">
-        <is>
-          <t>Deer</t>
-        </is>
-      </c>
-      <c r="E23" s="6" t="inlineStr">
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>Buck</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>Deer</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
         <is>
           <t>Muzzleloader</t>
         </is>
       </c>
-      <c r="F23" s="6" t="inlineStr">
-        <is>
-          <t>Limited Entry</t>
-        </is>
-      </c>
-      <c r="G23" s="6" t="inlineStr">
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t>Limited Entry</t>
+        </is>
+      </c>
+      <c r="G23" s="7" t="inlineStr">
         <is>
           <t>Oct 28 2026 - Nov 05 2026</t>
         </is>
       </c>
-      <c r="H23" s="6" t="inlineStr">
+      <c r="H23" s="8" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="I23" s="6" t="inlineStr">
+      <c r="I23" s="7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="J23" s="6" t="inlineStr">
+      <c r="J23" s="8" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="K23" s="6" t="inlineStr"/>
+      <c r="K23" s="7" t="n"/>
       <c r="L23" s="7" t="n">
         <v>2025</v>
       </c>
-      <c r="M23" s="7" t="inlineStr">
+      <c r="M23" s="8" t="inlineStr">
         <is>
           <t>53.3</t>
         </is>
       </c>
-      <c r="N23" s="7" t="inlineStr"/>
-      <c r="O23" s="7" t="inlineStr">
+      <c r="N23" s="8" t="n"/>
+      <c r="O23" s="8" t="inlineStr">
         <is>
           <t>6.7</t>
         </is>
       </c>
     </row>
     <row r="24" ht="24" customHeight="1">
-      <c r="A24" s="6" t="inlineStr">
+      <c r="A24" s="5" t="inlineStr">
         <is>
           <t>San Juan, Elk Ridge</t>
         </is>
       </c>
-      <c r="B24" s="6" t="inlineStr">
+      <c r="B24" s="5" t="inlineStr">
         <is>
           <t>DB1037</t>
         </is>
       </c>
-      <c r="C24" s="6" t="inlineStr">
-        <is>
-          <t>Buck</t>
-        </is>
-      </c>
-      <c r="D24" s="6" t="inlineStr">
-        <is>
-          <t>Deer</t>
-        </is>
-      </c>
-      <c r="E24" s="6" t="inlineStr">
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>Buck</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>Deer</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
         <is>
           <t>Muzzleloader</t>
         </is>
       </c>
-      <c r="F24" s="6" t="inlineStr">
-        <is>
-          <t>Limited Entry</t>
-        </is>
-      </c>
-      <c r="G24" s="6" t="inlineStr">
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>Limited Entry</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="inlineStr">
         <is>
           <t>Sept 23 2026 - Oct 01 2026</t>
         </is>
@@ -2116,7 +2145,7 @@
           <t>15</t>
         </is>
       </c>
-      <c r="I24" s="6" t="inlineStr">
+      <c r="I24" s="5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -2126,121 +2155,121 @@
           <t>17</t>
         </is>
       </c>
-      <c r="K24" s="6" t="inlineStr"/>
-      <c r="L24" s="7" t="n">
-        <v>2025</v>
-      </c>
-      <c r="M24" s="7" t="inlineStr">
+      <c r="K24" s="5" t="n"/>
+      <c r="L24" s="5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="M24" s="6" t="inlineStr">
         <is>
           <t>87.5</t>
         </is>
       </c>
-      <c r="N24" s="7" t="inlineStr"/>
-      <c r="O24" s="7" t="inlineStr">
+      <c r="N24" s="6" t="n"/>
+      <c r="O24" s="6" t="inlineStr">
         <is>
           <t>4.6</t>
         </is>
       </c>
     </row>
     <row r="25" ht="24" customHeight="1">
-      <c r="A25" s="6" t="inlineStr">
+      <c r="A25" s="7" t="inlineStr">
         <is>
           <t>Diamond Mtn</t>
         </is>
       </c>
-      <c r="B25" s="6" t="inlineStr">
+      <c r="B25" s="7" t="inlineStr">
         <is>
           <t>DB1038</t>
         </is>
       </c>
-      <c r="C25" s="6" t="inlineStr">
-        <is>
-          <t>Buck</t>
-        </is>
-      </c>
-      <c r="D25" s="6" t="inlineStr">
-        <is>
-          <t>Deer</t>
-        </is>
-      </c>
-      <c r="E25" s="6" t="inlineStr">
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>Buck</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>Deer</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
         <is>
           <t>Muzzleloader</t>
         </is>
       </c>
-      <c r="F25" s="6" t="inlineStr">
-        <is>
-          <t>Limited Entry</t>
-        </is>
-      </c>
-      <c r="G25" s="6" t="inlineStr">
+      <c r="F25" s="7" t="inlineStr">
+        <is>
+          <t>Limited Entry</t>
+        </is>
+      </c>
+      <c r="G25" s="7" t="inlineStr">
         <is>
           <t>Sept 23 2026 - Oct 01 2026</t>
         </is>
       </c>
-      <c r="H25" s="6" t="inlineStr">
+      <c r="H25" s="8" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="I25" s="6" t="inlineStr">
+      <c r="I25" s="7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="J25" s="6" t="inlineStr">
+      <c r="J25" s="8" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="K25" s="6" t="inlineStr"/>
+      <c r="K25" s="7" t="n"/>
       <c r="L25" s="7" t="n">
         <v>2025</v>
       </c>
-      <c r="M25" s="7" t="inlineStr">
+      <c r="M25" s="8" t="inlineStr">
         <is>
           <t>91.3</t>
         </is>
       </c>
-      <c r="N25" s="7" t="inlineStr"/>
-      <c r="O25" s="7" t="inlineStr">
+      <c r="N25" s="8" t="n"/>
+      <c r="O25" s="8" t="inlineStr">
         <is>
           <t>3.6</t>
         </is>
       </c>
     </row>
     <row r="26" ht="24" customHeight="1">
-      <c r="A26" s="6" t="inlineStr">
+      <c r="A26" s="5" t="inlineStr">
         <is>
           <t>Yellowstone</t>
         </is>
       </c>
-      <c r="B26" s="6" t="inlineStr">
+      <c r="B26" s="5" t="inlineStr">
         <is>
           <t>DB1039</t>
         </is>
       </c>
-      <c r="C26" s="6" t="inlineStr">
-        <is>
-          <t>Buck</t>
-        </is>
-      </c>
-      <c r="D26" s="6" t="inlineStr">
-        <is>
-          <t>Deer</t>
-        </is>
-      </c>
-      <c r="E26" s="6" t="inlineStr">
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>Buck</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>Deer</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
         <is>
           <t>Muzzleloader</t>
         </is>
       </c>
-      <c r="F26" s="6" t="inlineStr">
-        <is>
-          <t>Limited Entry</t>
-        </is>
-      </c>
-      <c r="G26" s="6" t="inlineStr">
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>Limited Entry</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="inlineStr">
         <is>
           <t>Oct 28 2026 - Nov 05 2026</t>
         </is>
@@ -2250,7 +2279,7 @@
           <t>6</t>
         </is>
       </c>
-      <c r="I26" s="6" t="inlineStr">
+      <c r="I26" s="5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -2260,121 +2289,121 @@
           <t>7</t>
         </is>
       </c>
-      <c r="K26" s="6" t="inlineStr"/>
-      <c r="L26" s="7" t="n">
-        <v>2025</v>
-      </c>
-      <c r="M26" s="7" t="inlineStr">
+      <c r="K26" s="5" t="n"/>
+      <c r="L26" s="5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="M26" s="6" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="N26" s="7" t="inlineStr"/>
-      <c r="O26" s="7" t="inlineStr">
+      <c r="N26" s="6" t="n"/>
+      <c r="O26" s="6" t="inlineStr">
         <is>
           <t>5.1</t>
         </is>
       </c>
     </row>
     <row r="27" ht="24" customHeight="1">
-      <c r="A27" s="6" t="inlineStr">
+      <c r="A27" s="7" t="inlineStr">
         <is>
           <t>Southwest Desert</t>
         </is>
       </c>
-      <c r="B27" s="6" t="inlineStr">
+      <c r="B27" s="7" t="inlineStr">
         <is>
           <t>DB1040</t>
         </is>
       </c>
-      <c r="C27" s="6" t="inlineStr">
-        <is>
-          <t>Buck</t>
-        </is>
-      </c>
-      <c r="D27" s="6" t="inlineStr">
-        <is>
-          <t>Deer</t>
-        </is>
-      </c>
-      <c r="E27" s="6" t="inlineStr">
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>Buck</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>Deer</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
         <is>
           <t>Muzzleloader</t>
         </is>
       </c>
-      <c r="F27" s="6" t="inlineStr">
-        <is>
-          <t>Limited Entry</t>
-        </is>
-      </c>
-      <c r="G27" s="6" t="inlineStr">
+      <c r="F27" s="7" t="inlineStr">
+        <is>
+          <t>Limited Entry</t>
+        </is>
+      </c>
+      <c r="G27" s="7" t="inlineStr">
         <is>
           <t>Oct 28 2026 - Nov 05 2026</t>
         </is>
       </c>
-      <c r="H27" s="6" t="inlineStr">
+      <c r="H27" s="8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="I27" s="6" t="inlineStr">
+      <c r="I27" s="7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="J27" s="6" t="inlineStr">
+      <c r="J27" s="8" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="K27" s="6" t="inlineStr"/>
+      <c r="K27" s="7" t="n"/>
       <c r="L27" s="7" t="n">
         <v>2025</v>
       </c>
-      <c r="M27" s="7" t="inlineStr">
+      <c r="M27" s="8" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="N27" s="7" t="inlineStr"/>
-      <c r="O27" s="7" t="inlineStr">
+      <c r="N27" s="8" t="n"/>
+      <c r="O27" s="8" t="inlineStr">
         <is>
           <t>7.4</t>
         </is>
       </c>
     </row>
     <row r="28" ht="24" customHeight="1">
-      <c r="A28" s="6" t="inlineStr">
+      <c r="A28" s="5" t="inlineStr">
         <is>
           <t>Wasatch Mtns, East</t>
         </is>
       </c>
-      <c r="B28" s="6" t="inlineStr">
+      <c r="B28" s="5" t="inlineStr">
         <is>
           <t>DB1041</t>
         </is>
       </c>
-      <c r="C28" s="6" t="inlineStr">
-        <is>
-          <t>Buck</t>
-        </is>
-      </c>
-      <c r="D28" s="6" t="inlineStr">
-        <is>
-          <t>Deer</t>
-        </is>
-      </c>
-      <c r="E28" s="6" t="inlineStr">
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>Buck</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>Deer</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
         <is>
           <t>Muzzleloader</t>
         </is>
       </c>
-      <c r="F28" s="6" t="inlineStr">
-        <is>
-          <t>Limited Entry</t>
-        </is>
-      </c>
-      <c r="G28" s="6" t="inlineStr">
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>Limited Entry</t>
+        </is>
+      </c>
+      <c r="G28" s="5" t="inlineStr">
         <is>
           <t>Oct 28 2026 - Nov 05 2026</t>
         </is>
@@ -2384,7 +2413,7 @@
           <t>30</t>
         </is>
       </c>
-      <c r="I28" s="6" t="inlineStr">
+      <c r="I28" s="5" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -2394,121 +2423,121 @@
           <t>33</t>
         </is>
       </c>
-      <c r="K28" s="6" t="inlineStr"/>
-      <c r="L28" s="7" t="n">
-        <v>2025</v>
-      </c>
-      <c r="M28" s="7" t="inlineStr">
+      <c r="K28" s="5" t="n"/>
+      <c r="L28" s="5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="M28" s="6" t="inlineStr">
         <is>
           <t>63.3</t>
         </is>
       </c>
-      <c r="N28" s="7" t="inlineStr"/>
-      <c r="O28" s="7" t="inlineStr">
+      <c r="N28" s="6" t="n"/>
+      <c r="O28" s="6" t="inlineStr">
         <is>
           <t>5.8</t>
         </is>
       </c>
     </row>
     <row r="29" ht="24" customHeight="1">
-      <c r="A29" s="6" t="inlineStr">
+      <c r="A29" s="7" t="inlineStr">
         <is>
           <t>West Desert, Vernon</t>
         </is>
       </c>
-      <c r="B29" s="6" t="inlineStr">
+      <c r="B29" s="7" t="inlineStr">
         <is>
           <t>DB1042</t>
         </is>
       </c>
-      <c r="C29" s="6" t="inlineStr">
-        <is>
-          <t>Buck</t>
-        </is>
-      </c>
-      <c r="D29" s="6" t="inlineStr">
-        <is>
-          <t>Deer</t>
-        </is>
-      </c>
-      <c r="E29" s="6" t="inlineStr">
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>Buck</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>Deer</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
         <is>
           <t>Muzzleloader</t>
         </is>
       </c>
-      <c r="F29" s="6" t="inlineStr">
-        <is>
-          <t>Limited Entry</t>
-        </is>
-      </c>
-      <c r="G29" s="6" t="inlineStr">
+      <c r="F29" s="7" t="inlineStr">
+        <is>
+          <t>Limited Entry</t>
+        </is>
+      </c>
+      <c r="G29" s="7" t="inlineStr">
         <is>
           <t>Sept 23 2026 - Oct 01 2026</t>
         </is>
       </c>
-      <c r="H29" s="6" t="inlineStr">
+      <c r="H29" s="8" t="inlineStr">
         <is>
           <t>46</t>
         </is>
       </c>
-      <c r="I29" s="6" t="inlineStr">
+      <c r="I29" s="7" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="J29" s="6" t="inlineStr">
+      <c r="J29" s="8" t="inlineStr">
         <is>
           <t>51</t>
         </is>
       </c>
-      <c r="K29" s="6" t="inlineStr"/>
+      <c r="K29" s="7" t="n"/>
       <c r="L29" s="7" t="n">
         <v>2025</v>
       </c>
-      <c r="M29" s="7" t="inlineStr">
+      <c r="M29" s="8" t="inlineStr">
         <is>
           <t>88</t>
         </is>
       </c>
-      <c r="N29" s="7" t="inlineStr"/>
-      <c r="O29" s="7" t="inlineStr">
+      <c r="N29" s="8" t="n"/>
+      <c r="O29" s="8" t="inlineStr">
         <is>
           <t>4.6</t>
         </is>
       </c>
     </row>
     <row r="30" ht="24" customHeight="1">
-      <c r="A30" s="6" t="inlineStr">
+      <c r="A30" s="5" t="inlineStr">
         <is>
           <t>Zion</t>
         </is>
       </c>
-      <c r="B30" s="6" t="inlineStr">
+      <c r="B30" s="5" t="inlineStr">
         <is>
           <t>DB1043</t>
         </is>
       </c>
-      <c r="C30" s="6" t="inlineStr">
-        <is>
-          <t>Buck</t>
-        </is>
-      </c>
-      <c r="D30" s="6" t="inlineStr">
-        <is>
-          <t>Deer</t>
-        </is>
-      </c>
-      <c r="E30" s="6" t="inlineStr">
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>Buck</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>Deer</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
         <is>
           <t>Muzzleloader</t>
         </is>
       </c>
-      <c r="F30" s="6" t="inlineStr">
-        <is>
-          <t>Limited Entry</t>
-        </is>
-      </c>
-      <c r="G30" s="6" t="inlineStr">
+      <c r="F30" s="5" t="inlineStr">
+        <is>
+          <t>Limited Entry</t>
+        </is>
+      </c>
+      <c r="G30" s="5" t="inlineStr">
         <is>
           <t>Oct 28 2026 - Nov 05 2026</t>
         </is>
@@ -2518,7 +2547,7 @@
           <t>15</t>
         </is>
       </c>
-      <c r="I30" s="6" t="inlineStr">
+      <c r="I30" s="5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -2528,121 +2557,121 @@
           <t>17</t>
         </is>
       </c>
-      <c r="K30" s="6" t="inlineStr"/>
-      <c r="L30" s="7" t="n">
-        <v>2025</v>
-      </c>
-      <c r="M30" s="7" t="inlineStr">
+      <c r="K30" s="5" t="n"/>
+      <c r="L30" s="5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="M30" s="6" t="inlineStr">
         <is>
           <t>46.7</t>
         </is>
       </c>
-      <c r="N30" s="7" t="inlineStr"/>
-      <c r="O30" s="7" t="inlineStr">
+      <c r="N30" s="6" t="n"/>
+      <c r="O30" s="6" t="inlineStr">
         <is>
           <t>6.4</t>
         </is>
       </c>
     </row>
     <row r="31" ht="24" customHeight="1">
-      <c r="A31" s="6" t="inlineStr">
+      <c r="A31" s="7" t="inlineStr">
         <is>
           <t>Book Cliffs</t>
         </is>
       </c>
-      <c r="B31" s="6" t="inlineStr">
+      <c r="B31" s="7" t="inlineStr">
         <is>
           <t>DB1044</t>
         </is>
       </c>
-      <c r="C31" s="6" t="inlineStr">
-        <is>
-          <t>Buck</t>
-        </is>
-      </c>
-      <c r="D31" s="6" t="inlineStr">
-        <is>
-          <t>Deer</t>
-        </is>
-      </c>
-      <c r="E31" s="6" t="inlineStr">
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t>Buck</t>
+        </is>
+      </c>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>Deer</t>
+        </is>
+      </c>
+      <c r="E31" s="7" t="inlineStr">
         <is>
           <t>Multiseason</t>
         </is>
       </c>
-      <c r="F31" s="6" t="inlineStr">
-        <is>
-          <t>Limited Entry</t>
-        </is>
-      </c>
-      <c r="G31" s="6" t="inlineStr">
+      <c r="F31" s="7" t="inlineStr">
+        <is>
+          <t>Limited Entry</t>
+        </is>
+      </c>
+      <c r="G31" s="7" t="inlineStr">
         <is>
           <t>Archery: Aug 15-Sept 11, 2026 | Muzz: Sept 23-Oct 1, 2026 | ALW: Oct 17-25, 2026</t>
         </is>
       </c>
-      <c r="H31" s="6" t="inlineStr">
+      <c r="H31" s="8" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="I31" s="6" t="inlineStr">
+      <c r="I31" s="7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="J31" s="6" t="inlineStr">
+      <c r="J31" s="8" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="K31" s="6" t="inlineStr"/>
+      <c r="K31" s="7" t="n"/>
       <c r="L31" s="7" t="n">
         <v>2025</v>
       </c>
-      <c r="M31" s="7" t="inlineStr">
+      <c r="M31" s="8" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="N31" s="7" t="inlineStr"/>
-      <c r="O31" s="7" t="inlineStr">
+      <c r="N31" s="8" t="n"/>
+      <c r="O31" s="8" t="inlineStr">
         <is>
           <t>15.3</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="34" customHeight="1">
-      <c r="A32" s="6" t="inlineStr">
+    <row r="32" ht="33.95" customHeight="1">
+      <c r="A32" s="5" t="inlineStr">
         <is>
           <t>Fillmore, Oak Creek LE</t>
         </is>
       </c>
-      <c r="B32" s="6" t="inlineStr">
+      <c r="B32" s="5" t="inlineStr">
         <is>
           <t>DB1045</t>
         </is>
       </c>
-      <c r="C32" s="6" t="inlineStr">
-        <is>
-          <t>Buck</t>
-        </is>
-      </c>
-      <c r="D32" s="6" t="inlineStr">
-        <is>
-          <t>Deer</t>
-        </is>
-      </c>
-      <c r="E32" s="6" t="inlineStr">
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>Buck</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>Deer</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
         <is>
           <t>Multiseason</t>
         </is>
       </c>
-      <c r="F32" s="6" t="inlineStr">
-        <is>
-          <t>Limited Entry</t>
-        </is>
-      </c>
-      <c r="G32" s="6" t="inlineStr">
+      <c r="F32" s="5" t="inlineStr">
+        <is>
+          <t>Limited Entry</t>
+        </is>
+      </c>
+      <c r="G32" s="5" t="inlineStr">
         <is>
           <t>Archery: Aug 15-Sept 11, 2026 | Muzz: Sept 23-Oct 1, 2026 | ALW: Oct 17-Oct 25, 2026</t>
         </is>
@@ -2652,7 +2681,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="I32" s="6" t="inlineStr">
+      <c r="I32" s="5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -2662,121 +2691,121 @@
           <t>2</t>
         </is>
       </c>
-      <c r="K32" s="6" t="inlineStr"/>
-      <c r="L32" s="7" t="n">
-        <v>2025</v>
-      </c>
-      <c r="M32" s="7" t="inlineStr">
+      <c r="K32" s="5" t="n"/>
+      <c r="L32" s="5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="M32" s="6" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="N32" s="7" t="inlineStr"/>
-      <c r="O32" s="7" t="inlineStr">
+      <c r="N32" s="6" t="n"/>
+      <c r="O32" s="6" t="inlineStr">
         <is>
           <t>30.3</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="34" customHeight="1">
-      <c r="A33" s="6" t="inlineStr">
+    <row r="33" ht="33.95" customHeight="1">
+      <c r="A33" s="7" t="inlineStr">
         <is>
           <t>San Juan, Elk Ridge</t>
         </is>
       </c>
-      <c r="B33" s="6" t="inlineStr">
+      <c r="B33" s="7" t="inlineStr">
         <is>
           <t>DB1046</t>
         </is>
       </c>
-      <c r="C33" s="6" t="inlineStr">
-        <is>
-          <t>Buck</t>
-        </is>
-      </c>
-      <c r="D33" s="6" t="inlineStr">
-        <is>
-          <t>Deer</t>
-        </is>
-      </c>
-      <c r="E33" s="6" t="inlineStr">
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>Buck</t>
+        </is>
+      </c>
+      <c r="D33" s="7" t="inlineStr">
+        <is>
+          <t>Deer</t>
+        </is>
+      </c>
+      <c r="E33" s="7" t="inlineStr">
         <is>
           <t>Multiseason</t>
         </is>
       </c>
-      <c r="F33" s="6" t="inlineStr">
-        <is>
-          <t>Limited Entry</t>
-        </is>
-      </c>
-      <c r="G33" s="6" t="inlineStr">
+      <c r="F33" s="7" t="inlineStr">
+        <is>
+          <t>Limited Entry</t>
+        </is>
+      </c>
+      <c r="G33" s="7" t="inlineStr">
         <is>
           <t>Archery: Aug 15-Sept 11, 2026 | Muzz: Sept 23-Oct 1, 2026 | ALW: Oct 17-Oct 25, 2026</t>
         </is>
       </c>
-      <c r="H33" s="6" t="inlineStr">
+      <c r="H33" s="8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I33" s="6" t="inlineStr">
+      <c r="I33" s="7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J33" s="6" t="inlineStr">
+      <c r="J33" s="8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K33" s="6" t="inlineStr"/>
+      <c r="K33" s="7" t="n"/>
       <c r="L33" s="7" t="n">
         <v>2025</v>
       </c>
-      <c r="M33" s="7" t="inlineStr">
+      <c r="M33" s="8" t="inlineStr">
         <is>
           <t>66.7</t>
         </is>
       </c>
-      <c r="N33" s="7" t="inlineStr"/>
-      <c r="O33" s="7" t="inlineStr">
+      <c r="N33" s="8" t="n"/>
+      <c r="O33" s="8" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="34" customHeight="1">
-      <c r="A34" s="6" t="inlineStr">
+    <row r="34" ht="33.95" customHeight="1">
+      <c r="A34" s="5" t="inlineStr">
         <is>
           <t>Diamond Mtn</t>
         </is>
       </c>
-      <c r="B34" s="6" t="inlineStr">
+      <c r="B34" s="5" t="inlineStr">
         <is>
           <t>DB1047</t>
         </is>
       </c>
-      <c r="C34" s="6" t="inlineStr">
-        <is>
-          <t>Buck</t>
-        </is>
-      </c>
-      <c r="D34" s="6" t="inlineStr">
-        <is>
-          <t>Deer</t>
-        </is>
-      </c>
-      <c r="E34" s="6" t="inlineStr">
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>Buck</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>Deer</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
         <is>
           <t>Multiseason</t>
         </is>
       </c>
-      <c r="F34" s="6" t="inlineStr">
-        <is>
-          <t>Limited Entry</t>
-        </is>
-      </c>
-      <c r="G34" s="6" t="inlineStr">
+      <c r="F34" s="5" t="inlineStr">
+        <is>
+          <t>Limited Entry</t>
+        </is>
+      </c>
+      <c r="G34" s="5" t="inlineStr">
         <is>
           <t>Archery: Aug 15-Sept 11, 2026 | Muzz: Sept 23-Oct 1, 2026 | ALW: Oct 17-Oct 25, 2026</t>
         </is>
@@ -2786,7 +2815,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="I34" s="6" t="inlineStr">
+      <c r="I34" s="5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -2796,121 +2825,121 @@
           <t>4</t>
         </is>
       </c>
-      <c r="K34" s="6" t="inlineStr"/>
-      <c r="L34" s="7" t="n">
-        <v>2025</v>
-      </c>
-      <c r="M34" s="7" t="inlineStr">
+      <c r="K34" s="5" t="n"/>
+      <c r="L34" s="5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="M34" s="6" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="N34" s="7" t="inlineStr"/>
-      <c r="O34" s="7" t="inlineStr">
+      <c r="N34" s="6" t="n"/>
+      <c r="O34" s="6" t="inlineStr">
         <is>
           <t>7.6</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="34" customHeight="1">
-      <c r="A35" s="6" t="inlineStr">
+    <row r="35" ht="33.95" customHeight="1">
+      <c r="A35" s="7" t="inlineStr">
         <is>
           <t>West Desert, Vernon</t>
         </is>
       </c>
-      <c r="B35" s="6" t="inlineStr">
+      <c r="B35" s="7" t="inlineStr">
         <is>
           <t>DB1048</t>
         </is>
       </c>
-      <c r="C35" s="6" t="inlineStr">
-        <is>
-          <t>Buck</t>
-        </is>
-      </c>
-      <c r="D35" s="6" t="inlineStr">
-        <is>
-          <t>Deer</t>
-        </is>
-      </c>
-      <c r="E35" s="6" t="inlineStr">
+      <c r="C35" s="7" t="inlineStr">
+        <is>
+          <t>Buck</t>
+        </is>
+      </c>
+      <c r="D35" s="7" t="inlineStr">
+        <is>
+          <t>Deer</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
         <is>
           <t>Multiseason</t>
         </is>
       </c>
-      <c r="F35" s="6" t="inlineStr">
-        <is>
-          <t>Limited Entry</t>
-        </is>
-      </c>
-      <c r="G35" s="6" t="inlineStr">
+      <c r="F35" s="7" t="inlineStr">
+        <is>
+          <t>Limited Entry</t>
+        </is>
+      </c>
+      <c r="G35" s="7" t="inlineStr">
         <is>
           <t>Archery: Aug 15-Sept 11, 2026 | Muzz: Sept 23-Oct 1, 2026 | ALW: Oct 17-Oct 25, 2026</t>
         </is>
       </c>
-      <c r="H35" s="6" t="inlineStr">
+      <c r="H35" s="8" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="I35" s="6" t="inlineStr">
+      <c r="I35" s="7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="J35" s="6" t="inlineStr">
+      <c r="J35" s="8" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="K35" s="6" t="inlineStr"/>
+      <c r="K35" s="7" t="n"/>
       <c r="L35" s="7" t="n">
         <v>2025</v>
       </c>
-      <c r="M35" s="7" t="inlineStr">
+      <c r="M35" s="8" t="inlineStr">
         <is>
           <t>77.8</t>
         </is>
       </c>
-      <c r="N35" s="7" t="inlineStr"/>
-      <c r="O35" s="7" t="inlineStr">
+      <c r="N35" s="8" t="n"/>
+      <c r="O35" s="8" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
     </row>
     <row r="36" ht="24" customHeight="1">
-      <c r="A36" s="6" t="inlineStr">
+      <c r="A36" s="5" t="inlineStr">
         <is>
           <t>Mt Dutton</t>
         </is>
       </c>
-      <c r="B36" s="6" t="inlineStr">
+      <c r="B36" s="5" t="inlineStr">
         <is>
           <t>DB1053</t>
         </is>
       </c>
-      <c r="C36" s="6" t="inlineStr">
-        <is>
-          <t>Buck</t>
-        </is>
-      </c>
-      <c r="D36" s="6" t="inlineStr">
-        <is>
-          <t>Deer</t>
-        </is>
-      </c>
-      <c r="E36" s="6" t="inlineStr">
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>Buck</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>Deer</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
         <is>
           <t>Muzzleloader</t>
         </is>
       </c>
-      <c r="F36" s="6" t="inlineStr">
-        <is>
-          <t>Limited Entry</t>
-        </is>
-      </c>
-      <c r="G36" s="6" t="inlineStr">
+      <c r="F36" s="5" t="inlineStr">
+        <is>
+          <t>Limited Entry</t>
+        </is>
+      </c>
+      <c r="G36" s="5" t="inlineStr">
         <is>
           <t>Oct 28 2026 - Nov 05 2026</t>
         </is>
@@ -2920,7 +2949,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="I36" s="6" t="inlineStr">
+      <c r="I36" s="5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -2930,121 +2959,121 @@
           <t>5</t>
         </is>
       </c>
-      <c r="K36" s="6" t="inlineStr"/>
-      <c r="L36" s="7" t="n">
-        <v>2025</v>
-      </c>
-      <c r="M36" s="7" t="inlineStr">
+      <c r="K36" s="5" t="n"/>
+      <c r="L36" s="5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="M36" s="6" t="inlineStr">
         <is>
           <t>80</t>
         </is>
       </c>
-      <c r="N36" s="7" t="inlineStr"/>
-      <c r="O36" s="7" t="inlineStr">
+      <c r="N36" s="6" t="n"/>
+      <c r="O36" s="6" t="inlineStr">
         <is>
           <t>6.5</t>
         </is>
       </c>
     </row>
     <row r="37" ht="24" customHeight="1">
-      <c r="A37" s="6" t="inlineStr">
+      <c r="A37" s="7" t="inlineStr">
         <is>
           <t>Ogden</t>
         </is>
       </c>
-      <c r="B37" s="6" t="inlineStr">
+      <c r="B37" s="7" t="inlineStr">
         <is>
           <t>DB1054</t>
         </is>
       </c>
-      <c r="C37" s="6" t="inlineStr">
-        <is>
-          <t>Buck</t>
-        </is>
-      </c>
-      <c r="D37" s="6" t="inlineStr">
-        <is>
-          <t>Deer</t>
-        </is>
-      </c>
-      <c r="E37" s="6" t="inlineStr">
+      <c r="C37" s="7" t="inlineStr">
+        <is>
+          <t>Buck</t>
+        </is>
+      </c>
+      <c r="D37" s="7" t="inlineStr">
+        <is>
+          <t>Deer</t>
+        </is>
+      </c>
+      <c r="E37" s="7" t="inlineStr">
         <is>
           <t>Muzzleloader</t>
         </is>
       </c>
-      <c r="F37" s="6" t="inlineStr">
-        <is>
-          <t>Limited Entry</t>
-        </is>
-      </c>
-      <c r="G37" s="6" t="inlineStr">
+      <c r="F37" s="7" t="inlineStr">
+        <is>
+          <t>Limited Entry</t>
+        </is>
+      </c>
+      <c r="G37" s="7" t="inlineStr">
         <is>
           <t>Oct 28 2026 - Nov 05 2026</t>
         </is>
       </c>
-      <c r="H37" s="6" t="inlineStr">
+      <c r="H37" s="8" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="I37" s="6" t="inlineStr">
+      <c r="I37" s="7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="J37" s="6" t="inlineStr">
+      <c r="J37" s="8" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="K37" s="6" t="inlineStr"/>
+      <c r="K37" s="7" t="n"/>
       <c r="L37" s="7" t="n">
         <v>2025</v>
       </c>
-      <c r="M37" s="7" t="inlineStr">
+      <c r="M37" s="8" t="inlineStr">
         <is>
           <t>54.5</t>
         </is>
       </c>
-      <c r="N37" s="7" t="inlineStr"/>
-      <c r="O37" s="7" t="inlineStr">
+      <c r="N37" s="8" t="n"/>
+      <c r="O37" s="8" t="inlineStr">
         <is>
           <t>6.8</t>
         </is>
       </c>
     </row>
     <row r="38" ht="24" customHeight="1">
-      <c r="A38" s="6" t="inlineStr">
+      <c r="A38" s="5" t="inlineStr">
         <is>
           <t>Fishlake</t>
         </is>
       </c>
-      <c r="B38" s="6" t="inlineStr">
+      <c r="B38" s="5" t="inlineStr">
         <is>
           <t>DB1055</t>
         </is>
       </c>
-      <c r="C38" s="6" t="inlineStr">
-        <is>
-          <t>Buck</t>
-        </is>
-      </c>
-      <c r="D38" s="6" t="inlineStr">
-        <is>
-          <t>Deer</t>
-        </is>
-      </c>
-      <c r="E38" s="6" t="inlineStr">
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>Buck</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>Deer</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
         <is>
           <t>Muzzleloader</t>
         </is>
       </c>
-      <c r="F38" s="6" t="inlineStr">
-        <is>
-          <t>Limited Entry</t>
-        </is>
-      </c>
-      <c r="G38" s="6" t="inlineStr">
+      <c r="F38" s="5" t="inlineStr">
+        <is>
+          <t>Limited Entry</t>
+        </is>
+      </c>
+      <c r="G38" s="5" t="inlineStr">
         <is>
           <t>Oct 28 2026 - Nov 05 2026</t>
         </is>
@@ -3054,7 +3083,7 @@
           <t>6</t>
         </is>
       </c>
-      <c r="I38" s="6" t="inlineStr">
+      <c r="I38" s="5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -3064,121 +3093,121 @@
           <t>7</t>
         </is>
       </c>
-      <c r="K38" s="6" t="inlineStr"/>
-      <c r="L38" s="7" t="n">
-        <v>2025</v>
-      </c>
-      <c r="M38" s="7" t="inlineStr">
+      <c r="K38" s="5" t="n"/>
+      <c r="L38" s="5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="M38" s="6" t="inlineStr">
         <is>
           <t>66.7</t>
         </is>
       </c>
-      <c r="N38" s="7" t="inlineStr"/>
-      <c r="O38" s="7" t="inlineStr">
+      <c r="N38" s="6" t="n"/>
+      <c r="O38" s="6" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
     </row>
     <row r="39" ht="24" customHeight="1">
-      <c r="A39" s="6" t="inlineStr">
+      <c r="A39" s="7" t="inlineStr">
         <is>
           <t>North Slope</t>
         </is>
       </c>
-      <c r="B39" s="6" t="inlineStr">
+      <c r="B39" s="7" t="inlineStr">
         <is>
           <t>DB1065</t>
         </is>
       </c>
-      <c r="C39" s="6" t="inlineStr">
-        <is>
-          <t>Buck</t>
-        </is>
-      </c>
-      <c r="D39" s="6" t="inlineStr">
-        <is>
-          <t>Deer</t>
-        </is>
-      </c>
-      <c r="E39" s="6" t="inlineStr">
+      <c r="C39" s="7" t="inlineStr">
+        <is>
+          <t>Buck</t>
+        </is>
+      </c>
+      <c r="D39" s="7" t="inlineStr">
+        <is>
+          <t>Deer</t>
+        </is>
+      </c>
+      <c r="E39" s="7" t="inlineStr">
         <is>
           <t>Muzzleloader</t>
         </is>
       </c>
-      <c r="F39" s="6" t="inlineStr">
-        <is>
-          <t>Limited Entry</t>
-        </is>
-      </c>
-      <c r="G39" s="6" t="inlineStr">
+      <c r="F39" s="7" t="inlineStr">
+        <is>
+          <t>Limited Entry</t>
+        </is>
+      </c>
+      <c r="G39" s="7" t="inlineStr">
         <is>
           <t>Oct 28 2026 - Nov 05 2026</t>
         </is>
       </c>
-      <c r="H39" s="6" t="inlineStr">
+      <c r="H39" s="8" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="I39" s="6" t="inlineStr">
+      <c r="I39" s="7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="J39" s="6" t="inlineStr">
+      <c r="J39" s="8" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="K39" s="6" t="inlineStr"/>
+      <c r="K39" s="7" t="n"/>
       <c r="L39" s="7" t="n">
         <v>2025</v>
       </c>
-      <c r="M39" s="7" t="inlineStr">
+      <c r="M39" s="8" t="inlineStr">
         <is>
           <t>80</t>
         </is>
       </c>
-      <c r="N39" s="7" t="inlineStr"/>
-      <c r="O39" s="7" t="inlineStr">
+      <c r="N39" s="8" t="n"/>
+      <c r="O39" s="8" t="inlineStr">
         <is>
           <t>5.8</t>
         </is>
       </c>
     </row>
     <row r="40" ht="24" customHeight="1">
-      <c r="A40" s="6" t="inlineStr">
+      <c r="A40" s="5" t="inlineStr">
         <is>
           <t>Box Elder</t>
         </is>
       </c>
-      <c r="B40" s="6" t="inlineStr">
+      <c r="B40" s="5" t="inlineStr">
         <is>
           <t>DB1077</t>
         </is>
       </c>
-      <c r="C40" s="6" t="inlineStr">
-        <is>
-          <t>Buck</t>
-        </is>
-      </c>
-      <c r="D40" s="6" t="inlineStr">
-        <is>
-          <t>Deer</t>
-        </is>
-      </c>
-      <c r="E40" s="6" t="inlineStr">
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>Buck</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t>Deer</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
         <is>
           <t>Muzzleloader</t>
         </is>
       </c>
-      <c r="F40" s="6" t="inlineStr">
-        <is>
-          <t>Limited Entry</t>
-        </is>
-      </c>
-      <c r="G40" s="6" t="inlineStr">
+      <c r="F40" s="5" t="inlineStr">
+        <is>
+          <t>Limited Entry</t>
+        </is>
+      </c>
+      <c r="G40" s="5" t="inlineStr">
         <is>
           <t>Oct 28 2026 - Nov 05 2026</t>
         </is>
@@ -3188,7 +3217,7 @@
           <t>23</t>
         </is>
       </c>
-      <c r="I40" s="6" t="inlineStr">
+      <c r="I40" s="5" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -3198,121 +3227,121 @@
           <t>26</t>
         </is>
       </c>
-      <c r="K40" s="6" t="inlineStr"/>
-      <c r="L40" s="7" t="n">
-        <v>2025</v>
-      </c>
-      <c r="M40" s="7" t="inlineStr">
+      <c r="K40" s="5" t="n"/>
+      <c r="L40" s="5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="M40" s="6" t="inlineStr">
         <is>
           <t>56.5</t>
         </is>
       </c>
-      <c r="N40" s="7" t="inlineStr"/>
-      <c r="O40" s="7" t="inlineStr">
+      <c r="N40" s="6" t="n"/>
+      <c r="O40" s="6" t="inlineStr">
         <is>
           <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="41" ht="24" customHeight="1">
-      <c r="A41" s="6" t="inlineStr">
+      <c r="A41" s="7" t="inlineStr">
         <is>
           <t>Cache</t>
         </is>
       </c>
-      <c r="B41" s="6" t="inlineStr">
+      <c r="B41" s="7" t="inlineStr">
         <is>
           <t>DB1078</t>
         </is>
       </c>
-      <c r="C41" s="6" t="inlineStr">
-        <is>
-          <t>Buck</t>
-        </is>
-      </c>
-      <c r="D41" s="6" t="inlineStr">
-        <is>
-          <t>Deer</t>
-        </is>
-      </c>
-      <c r="E41" s="6" t="inlineStr">
+      <c r="C41" s="7" t="inlineStr">
+        <is>
+          <t>Buck</t>
+        </is>
+      </c>
+      <c r="D41" s="7" t="inlineStr">
+        <is>
+          <t>Deer</t>
+        </is>
+      </c>
+      <c r="E41" s="7" t="inlineStr">
         <is>
           <t>Muzzleloader</t>
         </is>
       </c>
-      <c r="F41" s="6" t="inlineStr">
-        <is>
-          <t>Limited Entry</t>
-        </is>
-      </c>
-      <c r="G41" s="6" t="inlineStr">
+      <c r="F41" s="7" t="inlineStr">
+        <is>
+          <t>Limited Entry</t>
+        </is>
+      </c>
+      <c r="G41" s="7" t="inlineStr">
         <is>
           <t>Oct 28 2026 - Nov 05 2026</t>
         </is>
       </c>
-      <c r="H41" s="6" t="inlineStr">
+      <c r="H41" s="8" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="I41" s="6" t="inlineStr">
+      <c r="I41" s="7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="J41" s="6" t="inlineStr">
+      <c r="J41" s="8" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="K41" s="6" t="inlineStr"/>
+      <c r="K41" s="7" t="n"/>
       <c r="L41" s="7" t="n">
         <v>2025</v>
       </c>
-      <c r="M41" s="7" t="inlineStr">
+      <c r="M41" s="8" t="inlineStr">
         <is>
           <t>80</t>
         </is>
       </c>
-      <c r="N41" s="7" t="inlineStr"/>
-      <c r="O41" s="7" t="inlineStr">
+      <c r="N41" s="8" t="n"/>
+      <c r="O41" s="8" t="inlineStr">
         <is>
           <t>5.7</t>
         </is>
       </c>
     </row>
     <row r="42" ht="24" customHeight="1">
-      <c r="A42" s="6" t="inlineStr">
+      <c r="A42" s="5" t="inlineStr">
         <is>
           <t>Manti/San Rafael</t>
         </is>
       </c>
-      <c r="B42" s="6" t="inlineStr">
+      <c r="B42" s="5" t="inlineStr">
         <is>
           <t>DB1079</t>
         </is>
       </c>
-      <c r="C42" s="6" t="inlineStr">
-        <is>
-          <t>Buck</t>
-        </is>
-      </c>
-      <c r="D42" s="6" t="inlineStr">
-        <is>
-          <t>Deer</t>
-        </is>
-      </c>
-      <c r="E42" s="6" t="inlineStr">
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>Buck</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="inlineStr">
+        <is>
+          <t>Deer</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
         <is>
           <t>Muzzleloader</t>
         </is>
       </c>
-      <c r="F42" s="6" t="inlineStr">
-        <is>
-          <t>Limited Entry</t>
-        </is>
-      </c>
-      <c r="G42" s="6" t="inlineStr">
+      <c r="F42" s="5" t="inlineStr">
+        <is>
+          <t>Limited Entry</t>
+        </is>
+      </c>
+      <c r="G42" s="5" t="inlineStr">
         <is>
           <t>Oct 28 2026 - Nov 05 2026</t>
         </is>
@@ -3322,7 +3351,7 @@
           <t>40</t>
         </is>
       </c>
-      <c r="I42" s="6" t="inlineStr">
+      <c r="I42" s="5" t="inlineStr">
         <is>
           <t>5</t>
         </is>
@@ -3332,121 +3361,121 @@
           <t>45</t>
         </is>
       </c>
-      <c r="K42" s="6" t="inlineStr"/>
-      <c r="L42" s="7" t="n">
-        <v>2025</v>
-      </c>
-      <c r="M42" s="7" t="inlineStr">
+      <c r="K42" s="5" t="n"/>
+      <c r="L42" s="5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="M42" s="6" t="inlineStr">
         <is>
           <t>82.5</t>
         </is>
       </c>
-      <c r="N42" s="7" t="inlineStr"/>
-      <c r="O42" s="7" t="inlineStr">
+      <c r="N42" s="6" t="n"/>
+      <c r="O42" s="6" t="inlineStr">
         <is>
           <t>5.5</t>
         </is>
       </c>
     </row>
     <row r="43" ht="24" customHeight="1">
-      <c r="A43" s="6" t="inlineStr">
+      <c r="A43" s="7" t="inlineStr">
         <is>
           <t>Nebo</t>
         </is>
       </c>
-      <c r="B43" s="6" t="inlineStr">
+      <c r="B43" s="7" t="inlineStr">
         <is>
           <t>DB1080</t>
         </is>
       </c>
-      <c r="C43" s="6" t="inlineStr">
-        <is>
-          <t>Buck</t>
-        </is>
-      </c>
-      <c r="D43" s="6" t="inlineStr">
-        <is>
-          <t>Deer</t>
-        </is>
-      </c>
-      <c r="E43" s="6" t="inlineStr">
+      <c r="C43" s="7" t="inlineStr">
+        <is>
+          <t>Buck</t>
+        </is>
+      </c>
+      <c r="D43" s="7" t="inlineStr">
+        <is>
+          <t>Deer</t>
+        </is>
+      </c>
+      <c r="E43" s="7" t="inlineStr">
         <is>
           <t>Muzzleloader</t>
         </is>
       </c>
-      <c r="F43" s="6" t="inlineStr">
-        <is>
-          <t>Limited Entry</t>
-        </is>
-      </c>
-      <c r="G43" s="6" t="inlineStr">
+      <c r="F43" s="7" t="inlineStr">
+        <is>
+          <t>Limited Entry</t>
+        </is>
+      </c>
+      <c r="G43" s="7" t="inlineStr">
         <is>
           <t>Oct 28 2026 - Nov 05 2026</t>
         </is>
       </c>
-      <c r="H43" s="6" t="inlineStr">
+      <c r="H43" s="8" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="I43" s="6" t="inlineStr">
+      <c r="I43" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="J43" s="6" t="inlineStr">
+      <c r="J43" s="8" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="K43" s="6" t="inlineStr"/>
+      <c r="K43" s="7" t="n"/>
       <c r="L43" s="7" t="n">
         <v>2025</v>
       </c>
-      <c r="M43" s="7" t="inlineStr">
+      <c r="M43" s="8" t="inlineStr">
         <is>
           <t>77.8</t>
         </is>
       </c>
-      <c r="N43" s="7" t="inlineStr"/>
-      <c r="O43" s="7" t="inlineStr">
+      <c r="N43" s="8" t="n"/>
+      <c r="O43" s="8" t="inlineStr">
         <is>
           <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="44" ht="24" customHeight="1">
-      <c r="A44" s="6" t="inlineStr">
+      <c r="A44" s="5" t="inlineStr">
         <is>
           <t>La Sal Mtns</t>
         </is>
       </c>
-      <c r="B44" s="6" t="inlineStr">
+      <c r="B44" s="5" t="inlineStr">
         <is>
           <t>DB1081</t>
         </is>
       </c>
-      <c r="C44" s="6" t="inlineStr">
-        <is>
-          <t>Buck</t>
-        </is>
-      </c>
-      <c r="D44" s="6" t="inlineStr">
-        <is>
-          <t>Deer</t>
-        </is>
-      </c>
-      <c r="E44" s="6" t="inlineStr">
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>Buck</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="inlineStr">
+        <is>
+          <t>Deer</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="inlineStr">
         <is>
           <t>Muzzleloader</t>
         </is>
       </c>
-      <c r="F44" s="6" t="inlineStr">
-        <is>
-          <t>Limited Entry</t>
-        </is>
-      </c>
-      <c r="G44" s="6" t="inlineStr">
+      <c r="F44" s="5" t="inlineStr">
+        <is>
+          <t>Limited Entry</t>
+        </is>
+      </c>
+      <c r="G44" s="5" t="inlineStr">
         <is>
           <t>Oct 28 2026 - Nov 05 2026</t>
         </is>
@@ -3456,7 +3485,7 @@
           <t>8</t>
         </is>
       </c>
-      <c r="I44" s="6" t="inlineStr">
+      <c r="I44" s="5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -3466,121 +3495,121 @@
           <t>9</t>
         </is>
       </c>
-      <c r="K44" s="6" t="inlineStr"/>
-      <c r="L44" s="7" t="n">
-        <v>2025</v>
-      </c>
-      <c r="M44" s="7" t="inlineStr">
+      <c r="K44" s="5" t="n"/>
+      <c r="L44" s="5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="M44" s="6" t="inlineStr">
         <is>
           <t>55.6</t>
         </is>
       </c>
-      <c r="N44" s="7" t="inlineStr"/>
-      <c r="O44" s="7" t="inlineStr">
+      <c r="N44" s="6" t="n"/>
+      <c r="O44" s="6" t="inlineStr">
         <is>
           <t>5.9</t>
         </is>
       </c>
     </row>
     <row r="45" ht="24" customHeight="1">
-      <c r="A45" s="6" t="inlineStr">
+      <c r="A45" s="7" t="inlineStr">
         <is>
           <t>Panguitch Lake</t>
         </is>
       </c>
-      <c r="B45" s="6" t="inlineStr">
+      <c r="B45" s="7" t="inlineStr">
         <is>
           <t>DB1083</t>
         </is>
       </c>
-      <c r="C45" s="6" t="inlineStr">
-        <is>
-          <t>Buck</t>
-        </is>
-      </c>
-      <c r="D45" s="6" t="inlineStr">
-        <is>
-          <t>Deer</t>
-        </is>
-      </c>
-      <c r="E45" s="6" t="inlineStr">
+      <c r="C45" s="7" t="inlineStr">
+        <is>
+          <t>Buck</t>
+        </is>
+      </c>
+      <c r="D45" s="7" t="inlineStr">
+        <is>
+          <t>Deer</t>
+        </is>
+      </c>
+      <c r="E45" s="7" t="inlineStr">
         <is>
           <t>Muzzleloader</t>
         </is>
       </c>
-      <c r="F45" s="6" t="inlineStr">
-        <is>
-          <t>Limited Entry</t>
-        </is>
-      </c>
-      <c r="G45" s="6" t="inlineStr">
+      <c r="F45" s="7" t="inlineStr">
+        <is>
+          <t>Limited Entry</t>
+        </is>
+      </c>
+      <c r="G45" s="7" t="inlineStr">
         <is>
           <t>Oct 28 2026 - Nov 05 2026</t>
         </is>
       </c>
-      <c r="H45" s="6" t="inlineStr">
+      <c r="H45" s="8" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="I45" s="6" t="inlineStr">
+      <c r="I45" s="7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="J45" s="6" t="inlineStr">
+      <c r="J45" s="8" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="K45" s="6" t="inlineStr"/>
+      <c r="K45" s="7" t="n"/>
       <c r="L45" s="7" t="n">
         <v>2025</v>
       </c>
-      <c r="M45" s="7" t="inlineStr">
+      <c r="M45" s="8" t="inlineStr">
         <is>
           <t>45.5</t>
         </is>
       </c>
-      <c r="N45" s="7" t="inlineStr"/>
-      <c r="O45" s="7" t="inlineStr">
+      <c r="N45" s="8" t="n"/>
+      <c r="O45" s="8" t="inlineStr">
         <is>
           <t>6.7</t>
         </is>
       </c>
     </row>
     <row r="46" ht="24" customHeight="1">
-      <c r="A46" s="6" t="inlineStr">
+      <c r="A46" s="5" t="inlineStr">
         <is>
           <t>Boulder/Kaiparowits</t>
         </is>
       </c>
-      <c r="B46" s="6" t="inlineStr">
+      <c r="B46" s="5" t="inlineStr">
         <is>
           <t>DB1084</t>
         </is>
       </c>
-      <c r="C46" s="6" t="inlineStr">
-        <is>
-          <t>Buck</t>
-        </is>
-      </c>
-      <c r="D46" s="6" t="inlineStr">
-        <is>
-          <t>Deer</t>
-        </is>
-      </c>
-      <c r="E46" s="6" t="inlineStr">
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>Buck</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
+        <is>
+          <t>Deer</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="inlineStr">
         <is>
           <t>Muzzleloader</t>
         </is>
       </c>
-      <c r="F46" s="6" t="inlineStr">
-        <is>
-          <t>Limited Entry</t>
-        </is>
-      </c>
-      <c r="G46" s="6" t="inlineStr">
+      <c r="F46" s="5" t="inlineStr">
+        <is>
+          <t>Limited Entry</t>
+        </is>
+      </c>
+      <c r="G46" s="5" t="inlineStr">
         <is>
           <t>Oct 28 2026 - Nov 05 2026</t>
         </is>
@@ -3590,7 +3619,7 @@
           <t>12</t>
         </is>
       </c>
-      <c r="I46" s="6" t="inlineStr">
+      <c r="I46" s="5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -3600,121 +3629,121 @@
           <t>13</t>
         </is>
       </c>
-      <c r="K46" s="6" t="inlineStr"/>
-      <c r="L46" s="7" t="n">
-        <v>2025</v>
-      </c>
-      <c r="M46" s="7" t="inlineStr">
+      <c r="K46" s="5" t="n"/>
+      <c r="L46" s="5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="M46" s="6" t="inlineStr">
         <is>
           <t>66.7</t>
         </is>
       </c>
-      <c r="N46" s="7" t="inlineStr"/>
-      <c r="O46" s="7" t="inlineStr">
+      <c r="N46" s="6" t="n"/>
+      <c r="O46" s="6" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
     </row>
     <row r="47" ht="24" customHeight="1">
-      <c r="A47" s="6" t="inlineStr">
+      <c r="A47" s="7" t="inlineStr">
         <is>
           <t>San Juan, Abajo Mtns</t>
         </is>
       </c>
-      <c r="B47" s="6" t="inlineStr">
+      <c r="B47" s="7" t="inlineStr">
         <is>
           <t>DB1085</t>
         </is>
       </c>
-      <c r="C47" s="6" t="inlineStr">
-        <is>
-          <t>Buck</t>
-        </is>
-      </c>
-      <c r="D47" s="6" t="inlineStr">
-        <is>
-          <t>Deer</t>
-        </is>
-      </c>
-      <c r="E47" s="6" t="inlineStr">
+      <c r="C47" s="7" t="inlineStr">
+        <is>
+          <t>Buck</t>
+        </is>
+      </c>
+      <c r="D47" s="7" t="inlineStr">
+        <is>
+          <t>Deer</t>
+        </is>
+      </c>
+      <c r="E47" s="7" t="inlineStr">
         <is>
           <t>Muzzleloader</t>
         </is>
       </c>
-      <c r="F47" s="6" t="inlineStr">
-        <is>
-          <t>Limited Entry</t>
-        </is>
-      </c>
-      <c r="G47" s="6" t="inlineStr">
+      <c r="F47" s="7" t="inlineStr">
+        <is>
+          <t>Limited Entry</t>
+        </is>
+      </c>
+      <c r="G47" s="7" t="inlineStr">
         <is>
           <t>Oct 28 2026 - Nov 05 2026</t>
         </is>
       </c>
-      <c r="H47" s="6" t="inlineStr">
+      <c r="H47" s="8" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="I47" s="6" t="inlineStr">
+      <c r="I47" s="7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="J47" s="6" t="inlineStr">
+      <c r="J47" s="8" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="K47" s="6" t="inlineStr"/>
+      <c r="K47" s="7" t="n"/>
       <c r="L47" s="7" t="n">
         <v>2025</v>
       </c>
-      <c r="M47" s="7" t="inlineStr">
+      <c r="M47" s="8" t="inlineStr">
         <is>
           <t>66.7</t>
         </is>
       </c>
-      <c r="N47" s="7" t="inlineStr"/>
-      <c r="O47" s="7" t="inlineStr">
+      <c r="N47" s="8" t="n"/>
+      <c r="O47" s="8" t="inlineStr">
         <is>
           <t>6.4</t>
         </is>
       </c>
     </row>
     <row r="48" ht="24" customHeight="1">
-      <c r="A48" s="6" t="inlineStr">
+      <c r="A48" s="5" t="inlineStr">
         <is>
           <t>Vernal/Bonanza</t>
         </is>
       </c>
-      <c r="B48" s="6" t="inlineStr">
+      <c r="B48" s="5" t="inlineStr">
         <is>
           <t>DB1086</t>
         </is>
       </c>
-      <c r="C48" s="6" t="inlineStr">
-        <is>
-          <t>Buck</t>
-        </is>
-      </c>
-      <c r="D48" s="6" t="inlineStr">
-        <is>
-          <t>Deer</t>
-        </is>
-      </c>
-      <c r="E48" s="6" t="inlineStr">
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>Buck</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="inlineStr">
+        <is>
+          <t>Deer</t>
+        </is>
+      </c>
+      <c r="E48" s="5" t="inlineStr">
         <is>
           <t>Muzzleloader</t>
         </is>
       </c>
-      <c r="F48" s="6" t="inlineStr">
-        <is>
-          <t>Limited Entry</t>
-        </is>
-      </c>
-      <c r="G48" s="6" t="inlineStr">
+      <c r="F48" s="5" t="inlineStr">
+        <is>
+          <t>Limited Entry</t>
+        </is>
+      </c>
+      <c r="G48" s="5" t="inlineStr">
         <is>
           <t>Oct 28 2026 - Nov 05 2026</t>
         </is>
@@ -3724,7 +3753,7 @@
           <t>6</t>
         </is>
       </c>
-      <c r="I48" s="6" t="inlineStr">
+      <c r="I48" s="5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -3734,121 +3763,121 @@
           <t>7</t>
         </is>
       </c>
-      <c r="K48" s="6" t="inlineStr"/>
-      <c r="L48" s="7" t="n">
-        <v>2025</v>
-      </c>
-      <c r="M48" s="7" t="inlineStr">
+      <c r="K48" s="5" t="n"/>
+      <c r="L48" s="5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="M48" s="6" t="inlineStr">
         <is>
           <t>80</t>
         </is>
       </c>
-      <c r="N48" s="7" t="inlineStr"/>
-      <c r="O48" s="7" t="inlineStr">
+      <c r="N48" s="6" t="n"/>
+      <c r="O48" s="6" t="inlineStr">
         <is>
           <t>3.3</t>
         </is>
       </c>
     </row>
     <row r="49" ht="24" customHeight="1">
-      <c r="A49" s="6" t="inlineStr">
+      <c r="A49" s="7" t="inlineStr">
         <is>
           <t>Wasatch Mtns, West</t>
         </is>
       </c>
-      <c r="B49" s="6" t="inlineStr">
+      <c r="B49" s="7" t="inlineStr">
         <is>
           <t>DB1087</t>
         </is>
       </c>
-      <c r="C49" s="6" t="inlineStr">
-        <is>
-          <t>Buck</t>
-        </is>
-      </c>
-      <c r="D49" s="6" t="inlineStr">
-        <is>
-          <t>Deer</t>
-        </is>
-      </c>
-      <c r="E49" s="6" t="inlineStr">
+      <c r="C49" s="7" t="inlineStr">
+        <is>
+          <t>Buck</t>
+        </is>
+      </c>
+      <c r="D49" s="7" t="inlineStr">
+        <is>
+          <t>Deer</t>
+        </is>
+      </c>
+      <c r="E49" s="7" t="inlineStr">
         <is>
           <t>Muzzleloader</t>
         </is>
       </c>
-      <c r="F49" s="6" t="inlineStr">
-        <is>
-          <t>Limited Entry</t>
-        </is>
-      </c>
-      <c r="G49" s="6" t="inlineStr">
+      <c r="F49" s="7" t="inlineStr">
+        <is>
+          <t>Limited Entry</t>
+        </is>
+      </c>
+      <c r="G49" s="7" t="inlineStr">
         <is>
           <t>Oct 28 2026 - Nov 05 2026</t>
         </is>
       </c>
-      <c r="H49" s="6" t="inlineStr">
+      <c r="H49" s="8" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="I49" s="6" t="inlineStr">
+      <c r="I49" s="7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J49" s="6" t="inlineStr">
+      <c r="J49" s="8" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="K49" s="6" t="inlineStr"/>
+      <c r="K49" s="7" t="n"/>
       <c r="L49" s="7" t="n">
         <v>2025</v>
       </c>
-      <c r="M49" s="7" t="inlineStr">
+      <c r="M49" s="8" t="inlineStr">
         <is>
           <t>66.7</t>
         </is>
       </c>
-      <c r="N49" s="7" t="inlineStr"/>
-      <c r="O49" s="7" t="inlineStr">
+      <c r="N49" s="8" t="n"/>
+      <c r="O49" s="8" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
     </row>
     <row r="50" ht="24" customHeight="1">
-      <c r="A50" s="6" t="inlineStr">
+      <c r="A50" s="5" t="inlineStr">
         <is>
           <t>Book Cliffs, Floy Canyon</t>
         </is>
       </c>
-      <c r="B50" s="6" t="inlineStr">
+      <c r="B50" s="5" t="inlineStr">
         <is>
           <t>DB1090</t>
         </is>
       </c>
-      <c r="C50" s="6" t="inlineStr">
-        <is>
-          <t>Buck</t>
-        </is>
-      </c>
-      <c r="D50" s="6" t="inlineStr">
-        <is>
-          <t>Deer</t>
-        </is>
-      </c>
-      <c r="E50" s="6" t="inlineStr">
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>Buck</t>
+        </is>
+      </c>
+      <c r="D50" s="5" t="inlineStr">
+        <is>
+          <t>Deer</t>
+        </is>
+      </c>
+      <c r="E50" s="5" t="inlineStr">
         <is>
           <t>HAMSS (Handgun, Archery, Muzzleloader, Shotgun or Straight-walled rifle)</t>
         </is>
       </c>
-      <c r="F50" s="6" t="inlineStr">
-        <is>
-          <t>Limited Entry</t>
-        </is>
-      </c>
-      <c r="G50" s="6" t="inlineStr">
+      <c r="F50" s="5" t="inlineStr">
+        <is>
+          <t>Limited Entry</t>
+        </is>
+      </c>
+      <c r="G50" s="5" t="inlineStr">
         <is>
           <t>Nov 07 2026 - Nov 30 2026</t>
         </is>
@@ -3858,7 +3887,7 @@
           <t>6</t>
         </is>
       </c>
-      <c r="I50" s="6" t="inlineStr">
+      <c r="I50" s="5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -3868,121 +3897,121 @@
           <t>7</t>
         </is>
       </c>
-      <c r="K50" s="6" t="inlineStr"/>
-      <c r="L50" s="7" t="n">
-        <v>2025</v>
-      </c>
-      <c r="M50" s="7" t="inlineStr">
+      <c r="K50" s="5" t="n"/>
+      <c r="L50" s="5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="M50" s="6" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="N50" s="7" t="inlineStr"/>
-      <c r="O50" s="7" t="inlineStr">
+      <c r="N50" s="6" t="n"/>
+      <c r="O50" s="6" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
     </row>
     <row r="51" ht="24" customHeight="1">
-      <c r="A51" s="6" t="inlineStr">
+      <c r="A51" s="7" t="inlineStr">
         <is>
           <t>Kaiparowits HAMSS</t>
         </is>
       </c>
-      <c r="B51" s="6" t="inlineStr">
+      <c r="B51" s="7" t="inlineStr">
         <is>
           <t>DB1091</t>
         </is>
       </c>
-      <c r="C51" s="6" t="inlineStr">
-        <is>
-          <t>Buck</t>
-        </is>
-      </c>
-      <c r="D51" s="6" t="inlineStr">
-        <is>
-          <t>Deer</t>
-        </is>
-      </c>
-      <c r="E51" s="6" t="inlineStr">
+      <c r="C51" s="7" t="inlineStr">
+        <is>
+          <t>Buck</t>
+        </is>
+      </c>
+      <c r="D51" s="7" t="inlineStr">
+        <is>
+          <t>Deer</t>
+        </is>
+      </c>
+      <c r="E51" s="7" t="inlineStr">
         <is>
           <t>HAMSS (Handgun, Archery, Muzzleloader, Shotgun or Straight-walled rifle)</t>
         </is>
       </c>
-      <c r="F51" s="6" t="inlineStr">
-        <is>
-          <t>Limited Entry</t>
-        </is>
-      </c>
-      <c r="G51" s="6" t="inlineStr">
+      <c r="F51" s="7" t="inlineStr">
+        <is>
+          <t>Limited Entry</t>
+        </is>
+      </c>
+      <c r="G51" s="7" t="inlineStr">
         <is>
           <t>Nov 07 2026 - Nov 30 2026</t>
         </is>
       </c>
-      <c r="H51" s="6" t="inlineStr">
+      <c r="H51" s="8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="I51" s="6" t="inlineStr">
+      <c r="I51" s="7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="J51" s="6" t="inlineStr">
+      <c r="J51" s="8" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="K51" s="6" t="inlineStr"/>
+      <c r="K51" s="7" t="n"/>
       <c r="L51" s="7" t="n">
         <v>2025</v>
       </c>
-      <c r="M51" s="7" t="inlineStr">
+      <c r="M51" s="8" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="N51" s="7" t="inlineStr"/>
-      <c r="O51" s="7" t="inlineStr">
+      <c r="N51" s="8" t="n"/>
+      <c r="O51" s="8" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
     </row>
     <row r="52" ht="24" customHeight="1">
-      <c r="A52" s="6" t="inlineStr">
+      <c r="A52" s="5" t="inlineStr">
         <is>
           <t>Chalk Creek</t>
         </is>
       </c>
-      <c r="B52" s="6" t="inlineStr">
+      <c r="B52" s="5" t="inlineStr">
         <is>
           <t>DB1100</t>
         </is>
       </c>
-      <c r="C52" s="6" t="inlineStr">
-        <is>
-          <t>Buck</t>
-        </is>
-      </c>
-      <c r="D52" s="6" t="inlineStr">
-        <is>
-          <t>Deer</t>
-        </is>
-      </c>
-      <c r="E52" s="6" t="inlineStr">
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>Buck</t>
+        </is>
+      </c>
+      <c r="D52" s="5" t="inlineStr">
+        <is>
+          <t>Deer</t>
+        </is>
+      </c>
+      <c r="E52" s="5" t="inlineStr">
         <is>
           <t>Muzzleloader</t>
         </is>
       </c>
-      <c r="F52" s="6" t="inlineStr">
-        <is>
-          <t>Limited Entry</t>
-        </is>
-      </c>
-      <c r="G52" s="6" t="inlineStr">
+      <c r="F52" s="5" t="inlineStr">
+        <is>
+          <t>Limited Entry</t>
+        </is>
+      </c>
+      <c r="G52" s="5" t="inlineStr">
         <is>
           <t>Oct 28 2026 - Nov 05 2026</t>
         </is>
@@ -3992,7 +4021,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="I52" s="6" t="inlineStr">
+      <c r="I52" s="5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -4002,121 +4031,121 @@
           <t>11</t>
         </is>
       </c>
-      <c r="K52" s="6" t="inlineStr"/>
-      <c r="L52" s="7" t="n">
-        <v>2025</v>
-      </c>
-      <c r="M52" s="7" t="inlineStr">
+      <c r="K52" s="5" t="n"/>
+      <c r="L52" s="5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="M52" s="6" t="inlineStr">
         <is>
           <t>81.8</t>
         </is>
       </c>
-      <c r="N52" s="7" t="inlineStr"/>
-      <c r="O52" s="7" t="inlineStr">
+      <c r="N52" s="6" t="n"/>
+      <c r="O52" s="6" t="inlineStr">
         <is>
           <t>3.8</t>
         </is>
       </c>
     </row>
     <row r="53" ht="24" customHeight="1">
-      <c r="A53" s="6" t="inlineStr">
+      <c r="A53" s="7" t="inlineStr">
         <is>
           <t>East Canyon</t>
         </is>
       </c>
-      <c r="B53" s="6" t="inlineStr">
+      <c r="B53" s="7" t="inlineStr">
         <is>
           <t>DB1101</t>
         </is>
       </c>
-      <c r="C53" s="6" t="inlineStr">
-        <is>
-          <t>Buck</t>
-        </is>
-      </c>
-      <c r="D53" s="6" t="inlineStr">
-        <is>
-          <t>Deer</t>
-        </is>
-      </c>
-      <c r="E53" s="6" t="inlineStr">
+      <c r="C53" s="7" t="inlineStr">
+        <is>
+          <t>Buck</t>
+        </is>
+      </c>
+      <c r="D53" s="7" t="inlineStr">
+        <is>
+          <t>Deer</t>
+        </is>
+      </c>
+      <c r="E53" s="7" t="inlineStr">
         <is>
           <t>Muzzleloader</t>
         </is>
       </c>
-      <c r="F53" s="6" t="inlineStr">
-        <is>
-          <t>Limited Entry</t>
-        </is>
-      </c>
-      <c r="G53" s="6" t="inlineStr">
+      <c r="F53" s="7" t="inlineStr">
+        <is>
+          <t>Limited Entry</t>
+        </is>
+      </c>
+      <c r="G53" s="7" t="inlineStr">
         <is>
           <t>Oct 28 2026 - Nov 05 2026</t>
         </is>
       </c>
-      <c r="H53" s="6" t="inlineStr">
+      <c r="H53" s="8" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="I53" s="6" t="inlineStr">
+      <c r="I53" s="7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="J53" s="6" t="inlineStr">
+      <c r="J53" s="8" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="K53" s="6" t="inlineStr"/>
+      <c r="K53" s="7" t="n"/>
       <c r="L53" s="7" t="n">
         <v>2025</v>
       </c>
-      <c r="M53" s="7" t="inlineStr">
+      <c r="M53" s="8" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="N53" s="7" t="inlineStr"/>
-      <c r="O53" s="7" t="inlineStr">
+      <c r="N53" s="8" t="n"/>
+      <c r="O53" s="8" t="inlineStr">
         <is>
           <t>5.3</t>
         </is>
       </c>
     </row>
     <row r="54" ht="24" customHeight="1">
-      <c r="A54" s="6" t="inlineStr">
+      <c r="A54" s="5" t="inlineStr">
         <is>
           <t>Morgan-South Rich</t>
         </is>
       </c>
-      <c r="B54" s="6" t="inlineStr">
+      <c r="B54" s="5" t="inlineStr">
         <is>
           <t>DB1103</t>
         </is>
       </c>
-      <c r="C54" s="6" t="inlineStr">
-        <is>
-          <t>Buck</t>
-        </is>
-      </c>
-      <c r="D54" s="6" t="inlineStr">
-        <is>
-          <t>Deer</t>
-        </is>
-      </c>
-      <c r="E54" s="6" t="inlineStr">
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>Buck</t>
+        </is>
+      </c>
+      <c r="D54" s="5" t="inlineStr">
+        <is>
+          <t>Deer</t>
+        </is>
+      </c>
+      <c r="E54" s="5" t="inlineStr">
         <is>
           <t>Muzzleloader</t>
         </is>
       </c>
-      <c r="F54" s="6" t="inlineStr">
-        <is>
-          <t>Limited Entry</t>
-        </is>
-      </c>
-      <c r="G54" s="6" t="inlineStr">
+      <c r="F54" s="5" t="inlineStr">
+        <is>
+          <t>Limited Entry</t>
+        </is>
+      </c>
+      <c r="G54" s="5" t="inlineStr">
         <is>
           <t>Oct 28 2026 - Nov 05 2026</t>
         </is>
@@ -4126,7 +4155,7 @@
           <t>7</t>
         </is>
       </c>
-      <c r="I54" s="6" t="inlineStr">
+      <c r="I54" s="5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -4136,121 +4165,121 @@
           <t>8</t>
         </is>
       </c>
-      <c r="K54" s="6" t="inlineStr"/>
-      <c r="L54" s="7" t="n">
-        <v>2025</v>
-      </c>
-      <c r="M54" s="7" t="inlineStr">
+      <c r="K54" s="5" t="n"/>
+      <c r="L54" s="5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="M54" s="6" t="inlineStr">
         <is>
           <t>37.5</t>
         </is>
       </c>
-      <c r="N54" s="7" t="inlineStr"/>
-      <c r="O54" s="7" t="inlineStr">
+      <c r="N54" s="6" t="n"/>
+      <c r="O54" s="6" t="inlineStr">
         <is>
           <t>4.1</t>
         </is>
       </c>
     </row>
     <row r="55" ht="24" customHeight="1">
-      <c r="A55" s="6" t="inlineStr">
+      <c r="A55" s="7" t="inlineStr">
         <is>
           <t>East Canyon</t>
         </is>
       </c>
-      <c r="B55" s="6" t="inlineStr">
+      <c r="B55" s="7" t="inlineStr">
         <is>
           <t>DB1105</t>
         </is>
       </c>
-      <c r="C55" s="6" t="inlineStr">
-        <is>
-          <t>Buck</t>
-        </is>
-      </c>
-      <c r="D55" s="6" t="inlineStr">
-        <is>
-          <t>Deer</t>
-        </is>
-      </c>
-      <c r="E55" s="6" t="inlineStr">
+      <c r="C55" s="7" t="inlineStr">
+        <is>
+          <t>Buck</t>
+        </is>
+      </c>
+      <c r="D55" s="7" t="inlineStr">
+        <is>
+          <t>Deer</t>
+        </is>
+      </c>
+      <c r="E55" s="7" t="inlineStr">
         <is>
           <t>HAMSS (Handgun, Archery, Muzzleloader, Shotgun or Straight-walled rifle)</t>
         </is>
       </c>
-      <c r="F55" s="6" t="inlineStr">
-        <is>
-          <t>Limited Entry</t>
-        </is>
-      </c>
-      <c r="G55" s="6" t="inlineStr">
+      <c r="F55" s="7" t="inlineStr">
+        <is>
+          <t>Limited Entry</t>
+        </is>
+      </c>
+      <c r="G55" s="7" t="inlineStr">
         <is>
           <t>Nov 07 2026 - Nov 30 2026</t>
         </is>
       </c>
-      <c r="H55" s="6" t="inlineStr">
+      <c r="H55" s="8" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I55" s="6" t="inlineStr">
+      <c r="I55" s="7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="J55" s="6" t="inlineStr">
+      <c r="J55" s="8" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="K55" s="6" t="inlineStr"/>
+      <c r="K55" s="7" t="n"/>
       <c r="L55" s="7" t="n">
         <v>2025</v>
       </c>
-      <c r="M55" s="7" t="inlineStr">
+      <c r="M55" s="8" t="inlineStr">
         <is>
           <t>83.3</t>
         </is>
       </c>
-      <c r="N55" s="7" t="inlineStr"/>
-      <c r="O55" s="7" t="inlineStr">
+      <c r="N55" s="8" t="n"/>
+      <c r="O55" s="8" t="inlineStr">
         <is>
           <t>6.5</t>
         </is>
       </c>
     </row>
     <row r="56" ht="24" customHeight="1">
-      <c r="A56" s="6" t="inlineStr">
+      <c r="A56" s="5" t="inlineStr">
         <is>
           <t>Thousand Lakes</t>
         </is>
       </c>
-      <c r="B56" s="6" t="inlineStr">
+      <c r="B56" s="5" t="inlineStr">
         <is>
           <t>DB1106</t>
         </is>
       </c>
-      <c r="C56" s="6" t="inlineStr">
-        <is>
-          <t>Buck</t>
-        </is>
-      </c>
-      <c r="D56" s="6" t="inlineStr">
-        <is>
-          <t>Deer</t>
-        </is>
-      </c>
-      <c r="E56" s="6" t="inlineStr">
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>Buck</t>
+        </is>
+      </c>
+      <c r="D56" s="5" t="inlineStr">
+        <is>
+          <t>Deer</t>
+        </is>
+      </c>
+      <c r="E56" s="5" t="inlineStr">
         <is>
           <t>Restricted Archery</t>
         </is>
       </c>
-      <c r="F56" s="6" t="inlineStr">
-        <is>
-          <t>Limited Entry</t>
-        </is>
-      </c>
-      <c r="G56" s="6" t="inlineStr">
+      <c r="F56" s="5" t="inlineStr">
+        <is>
+          <t>Limited Entry</t>
+        </is>
+      </c>
+      <c r="G56" s="5" t="inlineStr">
         <is>
           <t>Aug 15 2026 - Sept 11 2026</t>
         </is>
@@ -4260,7 +4289,7 @@
           <t>20</t>
         </is>
       </c>
-      <c r="I56" s="6" t="inlineStr">
+      <c r="I56" s="5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -4270,121 +4299,121 @@
           <t>22</t>
         </is>
       </c>
-      <c r="K56" s="6" t="inlineStr"/>
-      <c r="L56" s="7" t="n">
-        <v>2025</v>
-      </c>
-      <c r="M56" s="7" t="inlineStr">
+      <c r="K56" s="5" t="n"/>
+      <c r="L56" s="5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="M56" s="6" t="inlineStr">
         <is>
           <t>16.7</t>
         </is>
       </c>
-      <c r="N56" s="7" t="inlineStr"/>
-      <c r="O56" s="7" t="inlineStr">
+      <c r="N56" s="6" t="n"/>
+      <c r="O56" s="6" t="inlineStr">
         <is>
           <t>5.3</t>
         </is>
       </c>
     </row>
     <row r="57" ht="24" customHeight="1">
-      <c r="A57" s="6" t="inlineStr">
+      <c r="A57" s="7" t="inlineStr">
         <is>
           <t>Thousand Lakes</t>
         </is>
       </c>
-      <c r="B57" s="6" t="inlineStr">
+      <c r="B57" s="7" t="inlineStr">
         <is>
           <t>DB1107</t>
         </is>
       </c>
-      <c r="C57" s="6" t="inlineStr">
-        <is>
-          <t>Buck</t>
-        </is>
-      </c>
-      <c r="D57" s="6" t="inlineStr">
-        <is>
-          <t>Deer</t>
-        </is>
-      </c>
-      <c r="E57" s="6" t="inlineStr">
+      <c r="C57" s="7" t="inlineStr">
+        <is>
+          <t>Buck</t>
+        </is>
+      </c>
+      <c r="D57" s="7" t="inlineStr">
+        <is>
+          <t>Deer</t>
+        </is>
+      </c>
+      <c r="E57" s="7" t="inlineStr">
         <is>
           <t>Restricted Muzzleloader</t>
         </is>
       </c>
-      <c r="F57" s="6" t="inlineStr">
-        <is>
-          <t>Limited Entry</t>
-        </is>
-      </c>
-      <c r="G57" s="6" t="inlineStr">
+      <c r="F57" s="7" t="inlineStr">
+        <is>
+          <t>Limited Entry</t>
+        </is>
+      </c>
+      <c r="G57" s="7" t="inlineStr">
         <is>
           <t>Sept 23 2026 - Oct 01 2026</t>
         </is>
       </c>
-      <c r="H57" s="6" t="inlineStr">
+      <c r="H57" s="8" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="I57" s="6" t="inlineStr">
+      <c r="I57" s="7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="J57" s="6" t="inlineStr">
+      <c r="J57" s="8" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="K57" s="6" t="inlineStr"/>
+      <c r="K57" s="7" t="n"/>
       <c r="L57" s="7" t="n">
         <v>2025</v>
       </c>
-      <c r="M57" s="7" t="inlineStr">
+      <c r="M57" s="8" t="inlineStr">
         <is>
           <t>27.8</t>
         </is>
       </c>
-      <c r="N57" s="7" t="inlineStr"/>
-      <c r="O57" s="7" t="inlineStr">
+      <c r="N57" s="8" t="n"/>
+      <c r="O57" s="8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
     </row>
     <row r="58" ht="24" customHeight="1">
-      <c r="A58" s="6" t="inlineStr">
+      <c r="A58" s="5" t="inlineStr">
         <is>
           <t>Thousand Lakes</t>
         </is>
       </c>
-      <c r="B58" s="6" t="inlineStr">
+      <c r="B58" s="5" t="inlineStr">
         <is>
           <t>DB1108</t>
         </is>
       </c>
-      <c r="C58" s="6" t="inlineStr">
-        <is>
-          <t>Buck</t>
-        </is>
-      </c>
-      <c r="D58" s="6" t="inlineStr">
-        <is>
-          <t>Deer</t>
-        </is>
-      </c>
-      <c r="E58" s="6" t="inlineStr">
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>Buck</t>
+        </is>
+      </c>
+      <c r="D58" s="5" t="inlineStr">
+        <is>
+          <t>Deer</t>
+        </is>
+      </c>
+      <c r="E58" s="5" t="inlineStr">
         <is>
           <t>Restricted Rifle</t>
         </is>
       </c>
-      <c r="F58" s="6" t="inlineStr">
-        <is>
-          <t>Limited Entry</t>
-        </is>
-      </c>
-      <c r="G58" s="6" t="inlineStr">
+      <c r="F58" s="5" t="inlineStr">
+        <is>
+          <t>Limited Entry</t>
+        </is>
+      </c>
+      <c r="G58" s="5" t="inlineStr">
         <is>
           <t>Oct 17 2026 - Oct 25 2026</t>
         </is>
@@ -4394,7 +4423,7 @@
           <t>27</t>
         </is>
       </c>
-      <c r="I58" s="6" t="inlineStr">
+      <c r="I58" s="5" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -4404,121 +4433,121 @@
           <t>30</t>
         </is>
       </c>
-      <c r="K58" s="6" t="inlineStr"/>
-      <c r="L58" s="7" t="n">
-        <v>2025</v>
-      </c>
-      <c r="M58" s="7" t="inlineStr">
+      <c r="K58" s="5" t="n"/>
+      <c r="L58" s="5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="M58" s="6" t="inlineStr">
         <is>
           <t>54.5</t>
         </is>
       </c>
-      <c r="N58" s="7" t="inlineStr"/>
-      <c r="O58" s="7" t="inlineStr">
+      <c r="N58" s="6" t="n"/>
+      <c r="O58" s="6" t="inlineStr">
         <is>
           <t>3.8</t>
         </is>
       </c>
     </row>
-    <row r="59" ht="34" customHeight="1">
-      <c r="A59" s="6" t="inlineStr">
+    <row r="59" ht="33.95" customHeight="1">
+      <c r="A59" s="7" t="inlineStr">
         <is>
           <t>Thousand Lakes</t>
         </is>
       </c>
-      <c r="B59" s="6" t="inlineStr">
+      <c r="B59" s="7" t="inlineStr">
         <is>
           <t>DB1109</t>
         </is>
       </c>
-      <c r="C59" s="6" t="inlineStr">
-        <is>
-          <t>Buck</t>
-        </is>
-      </c>
-      <c r="D59" s="6" t="inlineStr">
-        <is>
-          <t>Deer</t>
-        </is>
-      </c>
-      <c r="E59" s="6" t="inlineStr">
+      <c r="C59" s="7" t="inlineStr">
+        <is>
+          <t>Buck</t>
+        </is>
+      </c>
+      <c r="D59" s="7" t="inlineStr">
+        <is>
+          <t>Deer</t>
+        </is>
+      </c>
+      <c r="E59" s="7" t="inlineStr">
         <is>
           <t>Restricted Multiseason</t>
         </is>
       </c>
-      <c r="F59" s="6" t="inlineStr">
-        <is>
-          <t>Limited Entry</t>
-        </is>
-      </c>
-      <c r="G59" s="6" t="inlineStr">
+      <c r="F59" s="7" t="inlineStr">
+        <is>
+          <t>Limited Entry</t>
+        </is>
+      </c>
+      <c r="G59" s="7" t="inlineStr">
         <is>
           <t>Archery: Aug 15-Sept 11, 2026 | Muzz: Sept 23-Oct 1, 2026 | ALW: Oct 17-Oct 25, 2026</t>
         </is>
       </c>
-      <c r="H59" s="6" t="inlineStr">
+      <c r="H59" s="8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I59" s="6" t="inlineStr">
+      <c r="I59" s="7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J59" s="6" t="inlineStr">
+      <c r="J59" s="8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K59" s="6" t="inlineStr"/>
+      <c r="K59" s="7" t="n"/>
       <c r="L59" s="7" t="n">
         <v>2025</v>
       </c>
-      <c r="M59" s="7" t="inlineStr">
+      <c r="M59" s="8" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="N59" s="7" t="inlineStr"/>
-      <c r="O59" s="7" t="inlineStr">
+      <c r="N59" s="8" t="n"/>
+      <c r="O59" s="8" t="inlineStr">
         <is>
           <t>3.5</t>
         </is>
       </c>
     </row>
     <row r="60" ht="24" customHeight="1">
-      <c r="A60" s="6" t="inlineStr">
+      <c r="A60" s="5" t="inlineStr">
         <is>
           <t>Beaver, East</t>
         </is>
       </c>
-      <c r="B60" s="6" t="inlineStr">
+      <c r="B60" s="5" t="inlineStr">
         <is>
           <t>DB1110</t>
         </is>
       </c>
-      <c r="C60" s="6" t="inlineStr">
-        <is>
-          <t>Buck</t>
-        </is>
-      </c>
-      <c r="D60" s="6" t="inlineStr">
-        <is>
-          <t>Deer</t>
-        </is>
-      </c>
-      <c r="E60" s="6" t="inlineStr">
+      <c r="C60" s="5" t="inlineStr">
+        <is>
+          <t>Buck</t>
+        </is>
+      </c>
+      <c r="D60" s="5" t="inlineStr">
+        <is>
+          <t>Deer</t>
+        </is>
+      </c>
+      <c r="E60" s="5" t="inlineStr">
         <is>
           <t>Muzzleloader</t>
         </is>
       </c>
-      <c r="F60" s="6" t="inlineStr">
-        <is>
-          <t>Limited Entry</t>
-        </is>
-      </c>
-      <c r="G60" s="6" t="inlineStr">
+      <c r="F60" s="5" t="inlineStr">
+        <is>
+          <t>Limited Entry</t>
+        </is>
+      </c>
+      <c r="G60" s="5" t="inlineStr">
         <is>
           <t>Oct 28 2026 - Nov 05 2026</t>
         </is>
@@ -4528,7 +4557,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="I60" s="6" t="inlineStr">
+      <c r="I60" s="5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -4538,121 +4567,121 @@
           <t>11</t>
         </is>
       </c>
-      <c r="K60" s="6" t="inlineStr"/>
-      <c r="L60" s="7" t="n">
-        <v>2025</v>
-      </c>
-      <c r="M60" s="7" t="inlineStr">
+      <c r="K60" s="5" t="n"/>
+      <c r="L60" s="5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="M60" s="6" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="N60" s="7" t="inlineStr"/>
-      <c r="O60" s="7" t="inlineStr">
+      <c r="N60" s="6" t="n"/>
+      <c r="O60" s="6" t="inlineStr">
         <is>
           <t>8.3</t>
         </is>
       </c>
     </row>
     <row r="61" ht="24" customHeight="1">
-      <c r="A61" s="6" t="inlineStr">
+      <c r="A61" s="7" t="inlineStr">
         <is>
           <t>Beaver, West</t>
         </is>
       </c>
-      <c r="B61" s="6" t="inlineStr">
+      <c r="B61" s="7" t="inlineStr">
         <is>
           <t>DB1111</t>
         </is>
       </c>
-      <c r="C61" s="6" t="inlineStr">
-        <is>
-          <t>Buck</t>
-        </is>
-      </c>
-      <c r="D61" s="6" t="inlineStr">
-        <is>
-          <t>Deer</t>
-        </is>
-      </c>
-      <c r="E61" s="6" t="inlineStr">
+      <c r="C61" s="7" t="inlineStr">
+        <is>
+          <t>Buck</t>
+        </is>
+      </c>
+      <c r="D61" s="7" t="inlineStr">
+        <is>
+          <t>Deer</t>
+        </is>
+      </c>
+      <c r="E61" s="7" t="inlineStr">
         <is>
           <t>Muzzleloader</t>
         </is>
       </c>
-      <c r="F61" s="6" t="inlineStr">
-        <is>
-          <t>Limited Entry</t>
-        </is>
-      </c>
-      <c r="G61" s="6" t="inlineStr">
+      <c r="F61" s="7" t="inlineStr">
+        <is>
+          <t>Limited Entry</t>
+        </is>
+      </c>
+      <c r="G61" s="7" t="inlineStr">
         <is>
           <t>Oct 28 2026 - Nov 05 2026</t>
         </is>
       </c>
-      <c r="H61" s="6" t="inlineStr">
+      <c r="H61" s="8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="I61" s="6" t="inlineStr">
+      <c r="I61" s="7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="J61" s="6" t="inlineStr">
+      <c r="J61" s="8" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="K61" s="6" t="inlineStr"/>
+      <c r="K61" s="7" t="n"/>
       <c r="L61" s="7" t="n">
         <v>2025</v>
       </c>
-      <c r="M61" s="7" t="inlineStr">
+      <c r="M61" s="8" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="N61" s="7" t="inlineStr"/>
-      <c r="O61" s="7" t="inlineStr">
+      <c r="N61" s="8" t="n"/>
+      <c r="O61" s="8" t="inlineStr">
         <is>
           <t>6.8</t>
         </is>
       </c>
     </row>
     <row r="62" ht="24" customHeight="1">
-      <c r="A62" s="6" t="inlineStr">
+      <c r="A62" s="5" t="inlineStr">
         <is>
           <t>West Desert, Swasey</t>
         </is>
       </c>
-      <c r="B62" s="6" t="inlineStr">
+      <c r="B62" s="5" t="inlineStr">
         <is>
           <t>DB1112</t>
         </is>
       </c>
-      <c r="C62" s="6" t="inlineStr">
-        <is>
-          <t>Buck</t>
-        </is>
-      </c>
-      <c r="D62" s="6" t="inlineStr">
-        <is>
-          <t>Deer</t>
-        </is>
-      </c>
-      <c r="E62" s="6" t="inlineStr">
+      <c r="C62" s="5" t="inlineStr">
+        <is>
+          <t>Buck</t>
+        </is>
+      </c>
+      <c r="D62" s="5" t="inlineStr">
+        <is>
+          <t>Deer</t>
+        </is>
+      </c>
+      <c r="E62" s="5" t="inlineStr">
         <is>
           <t>Muzzleloader</t>
         </is>
       </c>
-      <c r="F62" s="6" t="inlineStr">
-        <is>
-          <t>Limited Entry</t>
-        </is>
-      </c>
-      <c r="G62" s="6" t="inlineStr">
+      <c r="F62" s="5" t="inlineStr">
+        <is>
+          <t>Limited Entry</t>
+        </is>
+      </c>
+      <c r="G62" s="5" t="inlineStr">
         <is>
           <t>Oct 28 2026 - Nov 05 2026</t>
         </is>
@@ -4662,7 +4691,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="I62" s="6" t="inlineStr">
+      <c r="I62" s="5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -4672,121 +4701,121 @@
           <t>5</t>
         </is>
       </c>
-      <c r="K62" s="6" t="inlineStr"/>
-      <c r="L62" s="7" t="n">
-        <v>2025</v>
-      </c>
-      <c r="M62" s="7" t="inlineStr">
+      <c r="K62" s="5" t="n"/>
+      <c r="L62" s="5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="M62" s="6" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="N62" s="7" t="inlineStr"/>
-      <c r="O62" s="7" t="inlineStr">
+      <c r="N62" s="6" t="n"/>
+      <c r="O62" s="6" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
     </row>
     <row r="63" ht="24" customHeight="1">
-      <c r="A63" s="6" t="inlineStr">
+      <c r="A63" s="7" t="inlineStr">
         <is>
           <t>Oquirrh/Tintic</t>
         </is>
       </c>
-      <c r="B63" s="6" t="inlineStr">
+      <c r="B63" s="7" t="inlineStr">
         <is>
           <t>DB1113</t>
         </is>
       </c>
-      <c r="C63" s="6" t="inlineStr">
-        <is>
-          <t>Buck</t>
-        </is>
-      </c>
-      <c r="D63" s="6" t="inlineStr">
-        <is>
-          <t>Deer</t>
-        </is>
-      </c>
-      <c r="E63" s="6" t="inlineStr">
+      <c r="C63" s="7" t="inlineStr">
+        <is>
+          <t>Buck</t>
+        </is>
+      </c>
+      <c r="D63" s="7" t="inlineStr">
+        <is>
+          <t>Deer</t>
+        </is>
+      </c>
+      <c r="E63" s="7" t="inlineStr">
         <is>
           <t>Muzzleloader</t>
         </is>
       </c>
-      <c r="F63" s="6" t="inlineStr">
-        <is>
-          <t>Limited Entry</t>
-        </is>
-      </c>
-      <c r="G63" s="6" t="inlineStr">
+      <c r="F63" s="7" t="inlineStr">
+        <is>
+          <t>Limited Entry</t>
+        </is>
+      </c>
+      <c r="G63" s="7" t="inlineStr">
         <is>
           <t>Oct 28 2026 - Nov 05 2026</t>
         </is>
       </c>
-      <c r="H63" s="6" t="inlineStr">
+      <c r="H63" s="8" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="I63" s="6" t="inlineStr">
+      <c r="I63" s="7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="J63" s="6" t="inlineStr">
+      <c r="J63" s="8" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="K63" s="6" t="inlineStr"/>
+      <c r="K63" s="7" t="n"/>
       <c r="L63" s="7" t="n">
         <v>2025</v>
       </c>
-      <c r="M63" s="7" t="inlineStr">
+      <c r="M63" s="8" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="N63" s="7" t="inlineStr"/>
-      <c r="O63" s="7" t="inlineStr">
+      <c r="N63" s="8" t="n"/>
+      <c r="O63" s="8" t="inlineStr">
         <is>
           <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="64" ht="24" customHeight="1">
-      <c r="A64" s="6" t="inlineStr">
+      <c r="A64" s="5" t="inlineStr">
         <is>
           <t>Cedar/Stansbury</t>
         </is>
       </c>
-      <c r="B64" s="6" t="inlineStr">
+      <c r="B64" s="5" t="inlineStr">
         <is>
           <t>DB1114</t>
         </is>
       </c>
-      <c r="C64" s="6" t="inlineStr">
-        <is>
-          <t>Buck</t>
-        </is>
-      </c>
-      <c r="D64" s="6" t="inlineStr">
-        <is>
-          <t>Deer</t>
-        </is>
-      </c>
-      <c r="E64" s="6" t="inlineStr">
+      <c r="C64" s="5" t="inlineStr">
+        <is>
+          <t>Buck</t>
+        </is>
+      </c>
+      <c r="D64" s="5" t="inlineStr">
+        <is>
+          <t>Deer</t>
+        </is>
+      </c>
+      <c r="E64" s="5" t="inlineStr">
         <is>
           <t>Muzzleloader</t>
         </is>
       </c>
-      <c r="F64" s="6" t="inlineStr">
-        <is>
-          <t>Limited Entry</t>
-        </is>
-      </c>
-      <c r="G64" s="6" t="inlineStr">
+      <c r="F64" s="5" t="inlineStr">
+        <is>
+          <t>Limited Entry</t>
+        </is>
+      </c>
+      <c r="G64" s="5" t="inlineStr">
         <is>
           <t>Oct 28 2026 - Nov 05 2026</t>
         </is>
@@ -4796,7 +4825,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="I64" s="6" t="inlineStr">
+      <c r="I64" s="5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -4806,121 +4835,121 @@
           <t>6</t>
         </is>
       </c>
-      <c r="K64" s="6" t="inlineStr"/>
-      <c r="L64" s="7" t="n">
-        <v>2025</v>
-      </c>
-      <c r="M64" s="7" t="inlineStr">
+      <c r="K64" s="5" t="n"/>
+      <c r="L64" s="5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="M64" s="6" t="inlineStr">
         <is>
           <t>33.3</t>
         </is>
       </c>
-      <c r="N64" s="7" t="inlineStr"/>
-      <c r="O64" s="7" t="inlineStr">
+      <c r="N64" s="6" t="n"/>
+      <c r="O64" s="6" t="inlineStr">
         <is>
           <t>6.2</t>
         </is>
       </c>
     </row>
     <row r="65" ht="24" customHeight="1">
-      <c r="A65" s="6" t="inlineStr">
+      <c r="A65" s="7" t="inlineStr">
         <is>
           <t>Little Rockies</t>
         </is>
       </c>
-      <c r="B65" s="6" t="inlineStr">
+      <c r="B65" s="7" t="inlineStr">
         <is>
           <t>DB1115</t>
         </is>
       </c>
-      <c r="C65" s="6" t="inlineStr">
-        <is>
-          <t>Buck</t>
-        </is>
-      </c>
-      <c r="D65" s="6" t="inlineStr">
-        <is>
-          <t>Deer</t>
-        </is>
-      </c>
-      <c r="E65" s="6" t="inlineStr">
+      <c r="C65" s="7" t="inlineStr">
+        <is>
+          <t>Buck</t>
+        </is>
+      </c>
+      <c r="D65" s="7" t="inlineStr">
+        <is>
+          <t>Deer</t>
+        </is>
+      </c>
+      <c r="E65" s="7" t="inlineStr">
         <is>
           <t>Any Legal Weapon</t>
         </is>
       </c>
-      <c r="F65" s="6" t="inlineStr">
-        <is>
-          <t>Limited Entry</t>
-        </is>
-      </c>
-      <c r="G65" s="6" t="inlineStr">
+      <c r="F65" s="7" t="inlineStr">
+        <is>
+          <t>Limited Entry</t>
+        </is>
+      </c>
+      <c r="G65" s="7" t="inlineStr">
         <is>
           <t>Nov 07 2026 - Nov 30 2026</t>
         </is>
       </c>
-      <c r="H65" s="6" t="inlineStr">
+      <c r="H65" s="8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="I65" s="6" t="inlineStr">
+      <c r="I65" s="7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="J65" s="6" t="inlineStr">
+      <c r="J65" s="8" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="K65" s="6" t="inlineStr"/>
+      <c r="K65" s="7" t="n"/>
       <c r="L65" s="7" t="n">
         <v>2025</v>
       </c>
-      <c r="M65" s="7" t="inlineStr">
+      <c r="M65" s="8" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="N65" s="7" t="inlineStr"/>
-      <c r="O65" s="7" t="inlineStr">
+      <c r="N65" s="8" t="n"/>
+      <c r="O65" s="8" t="inlineStr">
         <is>
           <t>11.8</t>
         </is>
       </c>
     </row>
     <row r="66" ht="24" customHeight="1">
-      <c r="A66" s="6" t="inlineStr">
+      <c r="A66" s="5" t="inlineStr">
         <is>
           <t>San Juan, Mancos Mesa</t>
         </is>
       </c>
-      <c r="B66" s="6" t="inlineStr">
+      <c r="B66" s="5" t="inlineStr">
         <is>
           <t>DB1116</t>
         </is>
       </c>
-      <c r="C66" s="6" t="inlineStr">
-        <is>
-          <t>Buck</t>
-        </is>
-      </c>
-      <c r="D66" s="6" t="inlineStr">
-        <is>
-          <t>Deer</t>
-        </is>
-      </c>
-      <c r="E66" s="6" t="inlineStr">
+      <c r="C66" s="5" t="inlineStr">
+        <is>
+          <t>Buck</t>
+        </is>
+      </c>
+      <c r="D66" s="5" t="inlineStr">
+        <is>
+          <t>Deer</t>
+        </is>
+      </c>
+      <c r="E66" s="5" t="inlineStr">
         <is>
           <t>HAMSS (Handgun, Archery, Muzzleloader, Shotgun or Straight-walled rifle)</t>
         </is>
       </c>
-      <c r="F66" s="6" t="inlineStr">
-        <is>
-          <t>Limited Entry</t>
-        </is>
-      </c>
-      <c r="G66" s="6" t="inlineStr">
+      <c r="F66" s="5" t="inlineStr">
+        <is>
+          <t>Limited Entry</t>
+        </is>
+      </c>
+      <c r="G66" s="5" t="inlineStr">
         <is>
           <t>Nov 07 2026 - Nov 30 2026</t>
         </is>
@@ -4930,7 +4959,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="I66" s="6" t="inlineStr">
+      <c r="I66" s="5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -4940,121 +4969,121 @@
           <t>5</t>
         </is>
       </c>
-      <c r="K66" s="6" t="inlineStr"/>
-      <c r="L66" s="7" t="n">
-        <v>2025</v>
-      </c>
-      <c r="M66" s="7" t="inlineStr">
+      <c r="K66" s="5" t="n"/>
+      <c r="L66" s="5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="M66" s="6" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="N66" s="7" t="inlineStr"/>
-      <c r="O66" s="7" t="inlineStr">
+      <c r="N66" s="6" t="n"/>
+      <c r="O66" s="6" t="inlineStr">
         <is>
           <t>13.8</t>
         </is>
       </c>
     </row>
     <row r="67" ht="24" customHeight="1">
-      <c r="A67" s="6" t="inlineStr">
+      <c r="A67" s="7" t="inlineStr">
         <is>
           <t>Moab Valley</t>
         </is>
       </c>
-      <c r="B67" s="6" t="inlineStr">
+      <c r="B67" s="7" t="inlineStr">
         <is>
           <t>DB1119</t>
         </is>
       </c>
-      <c r="C67" s="6" t="inlineStr">
-        <is>
-          <t>Buck</t>
-        </is>
-      </c>
-      <c r="D67" s="6" t="inlineStr">
-        <is>
-          <t>Deer</t>
-        </is>
-      </c>
-      <c r="E67" s="6" t="inlineStr">
+      <c r="C67" s="7" t="inlineStr">
+        <is>
+          <t>Buck</t>
+        </is>
+      </c>
+      <c r="D67" s="7" t="inlineStr">
+        <is>
+          <t>Deer</t>
+        </is>
+      </c>
+      <c r="E67" s="7" t="inlineStr">
         <is>
           <t>Any Legal Weapon</t>
         </is>
       </c>
-      <c r="F67" s="6" t="inlineStr">
-        <is>
-          <t>Limited Entry</t>
-        </is>
-      </c>
-      <c r="G67" s="6" t="inlineStr">
+      <c r="F67" s="7" t="inlineStr">
+        <is>
+          <t>Limited Entry</t>
+        </is>
+      </c>
+      <c r="G67" s="7" t="inlineStr">
         <is>
           <t>Nov 07 2026 - Nov 22 2026</t>
         </is>
       </c>
-      <c r="H67" s="6" t="inlineStr">
+      <c r="H67" s="8" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="I67" s="6" t="inlineStr">
+      <c r="I67" s="7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="J67" s="6" t="inlineStr">
+      <c r="J67" s="8" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="K67" s="6" t="inlineStr"/>
+      <c r="K67" s="7" t="n"/>
       <c r="L67" s="7" t="n">
         <v>2025</v>
       </c>
-      <c r="M67" s="7" t="inlineStr">
+      <c r="M67" s="8" t="inlineStr">
         <is>
           <t>44.4</t>
         </is>
       </c>
-      <c r="N67" s="7" t="inlineStr"/>
-      <c r="O67" s="7" t="inlineStr">
+      <c r="N67" s="8" t="n"/>
+      <c r="O67" s="8" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
     </row>
     <row r="68" ht="24" customHeight="1">
-      <c r="A68" s="6" t="inlineStr">
+      <c r="A68" s="5" t="inlineStr">
         <is>
           <t>Castle Valley</t>
         </is>
       </c>
-      <c r="B68" s="6" t="inlineStr">
+      <c r="B68" s="5" t="inlineStr">
         <is>
           <t>DB1120</t>
         </is>
       </c>
-      <c r="C68" s="6" t="inlineStr">
-        <is>
-          <t>Buck</t>
-        </is>
-      </c>
-      <c r="D68" s="6" t="inlineStr">
-        <is>
-          <t>Deer</t>
-        </is>
-      </c>
-      <c r="E68" s="6" t="inlineStr">
+      <c r="C68" s="5" t="inlineStr">
+        <is>
+          <t>Buck</t>
+        </is>
+      </c>
+      <c r="D68" s="5" t="inlineStr">
+        <is>
+          <t>Deer</t>
+        </is>
+      </c>
+      <c r="E68" s="5" t="inlineStr">
         <is>
           <t>Any Legal Weapon</t>
         </is>
       </c>
-      <c r="F68" s="6" t="inlineStr">
-        <is>
-          <t>Limited Entry</t>
-        </is>
-      </c>
-      <c r="G68" s="6" t="inlineStr">
+      <c r="F68" s="5" t="inlineStr">
+        <is>
+          <t>Limited Entry</t>
+        </is>
+      </c>
+      <c r="G68" s="5" t="inlineStr">
         <is>
           <t>Nov 07 2026 - Nov 22 2026</t>
         </is>
@@ -5064,7 +5093,7 @@
           <t>13</t>
         </is>
       </c>
-      <c r="I68" s="6" t="inlineStr">
+      <c r="I68" s="5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -5074,17 +5103,17 @@
           <t>15</t>
         </is>
       </c>
-      <c r="K68" s="6" t="inlineStr"/>
-      <c r="L68" s="7" t="n">
-        <v>2025</v>
-      </c>
-      <c r="M68" s="7" t="inlineStr">
+      <c r="K68" s="5" t="n"/>
+      <c r="L68" s="5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="M68" s="6" t="inlineStr">
         <is>
           <t>80</t>
         </is>
       </c>
-      <c r="N68" s="7" t="inlineStr"/>
-      <c r="O68" s="7" t="inlineStr">
+      <c r="N68" s="6" t="n"/>
+      <c r="O68" s="6" t="inlineStr">
         <is>
           <t>5.9</t>
         </is>
@@ -5092,9 +5121,9 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:O68"/>
-  <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.25" right="0.25" top="0.35" bottom="0.35" header="0.15" footer="0.15"/>
-  <pageSetup orientation="portrait" paperSize="1" fitToHeight="0" fitToWidth="1"/>
+  <printOptions horizontalCentered="1" verticalCentered="0"/>
+  <pageMargins left="0.25" right="0.25" top="0.35" bottom="0.35" header="0.2" footer="0.2"/>
+  <pageSetup orientation="landscape" paperSize="1" fitToHeight="1" fitToWidth="1"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
